--- a/results/control_study_quick/statistics.xlsx
+++ b/results/control_study_quick/statistics.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="916" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="924" uniqueCount="170">
   <si>
     <t>controller</t>
   </si>
@@ -155,6 +155,15 @@
     <t>mean_step_runtime_us</t>
   </si>
   <si>
+    <t>simulation_runtime_seconds</t>
+  </si>
+  <si>
+    <t>controller_evaluation_count</t>
+  </si>
+  <si>
+    <t>controller_completed_count</t>
+  </si>
+  <si>
     <t>metric</t>
   </si>
   <si>
@@ -243,6 +252,12 @@
   </si>
   <si>
     <t>p_value</t>
+  </si>
+  <si>
+    <t>configured_group_count</t>
+  </si>
+  <si>
+    <t>analyzed_group_count</t>
   </si>
   <si>
     <t>first_controller</t>
@@ -564,33 +579,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
     <col min="2" max="2" width="26.000000" customWidth="true"/>
     <col min="3" max="3" width="12.000000" customWidth="true"/>
-    <col min="4" max="4" width="4.90625" customWidth="true"/>
-    <col min="5" max="5" width="7.08984375" customWidth="true"/>
-    <col min="6" max="6" width="16.81640625" customWidth="true"/>
+    <col min="4" max="4" width="12.000000" customWidth="true"/>
+    <col min="5" max="5" width="12.000000" customWidth="true"/>
+    <col min="6" max="6" width="22.000000" customWidth="true"/>
     <col min="7" max="7" width="20.000000" customWidth="true"/>
-    <col min="8" max="8" width="12.6328125" customWidth="true"/>
-    <col min="9" max="9" width="13.453125" customWidth="true"/>
-    <col min="10" max="10" width="17.7265625" customWidth="true"/>
-    <col min="11" max="11" width="17.54296875" customWidth="true"/>
+    <col min="8" max="8" width="17.000000" customWidth="true"/>
+    <col min="9" max="9" width="17.000000" customWidth="true"/>
+    <col min="10" max="10" width="21.000000" customWidth="true"/>
+    <col min="11" max="11" width="21.000000" customWidth="true"/>
     <col min="12" max="12" width="15.453125" customWidth="true"/>
-    <col min="13" max="13" width="19.1796875" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="21.453125" customWidth="true"/>
-    <col min="16" max="16" width="19.36328125" customWidth="true"/>
-    <col min="17" max="17" width="17.08984375" customWidth="true"/>
-    <col min="18" max="18" width="15.453125" customWidth="true"/>
-    <col min="19" max="19" width="15.453125" customWidth="true"/>
-    <col min="20" max="20" width="14.1796875" customWidth="true"/>
-    <col min="21" max="21" width="14.36328125" customWidth="true"/>
-    <col min="22" max="22" width="23.6328125" customWidth="true"/>
-    <col min="23" max="23" width="24.36328125" customWidth="true"/>
-    <col min="24" max="24" width="20.7265625" customWidth="true"/>
+    <col min="13" max="13" width="26.000000" customWidth="true"/>
+    <col min="14" max="14" width="17.000000" customWidth="true"/>
+    <col min="15" max="15" width="28.000000" customWidth="true"/>
+    <col min="16" max="16" width="26.000000" customWidth="true"/>
+    <col min="17" max="17" width="22.000000" customWidth="true"/>
+    <col min="18" max="18" width="18.000000" customWidth="true"/>
+    <col min="19" max="19" width="18.000000" customWidth="true"/>
+    <col min="20" max="20" width="19.000000" customWidth="true"/>
+    <col min="21" max="21" width="20.000000" customWidth="true"/>
+    <col min="22" max="22" width="29.000000" customWidth="true"/>
+    <col min="23" max="23" width="30.000000" customWidth="true"/>
+    <col min="24" max="24" width="24.000000" customWidth="true"/>
+    <col min="25" max="25" width="30.000000" customWidth="true"/>
+    <col min="26" max="26" width="31.000000" customWidth="true"/>
+    <col min="27" max="27" width="30.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,6 +684,15 @@
       <c r="X1" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="Y1" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -733,10 +760,19 @@
         <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>0.1082087</v>
+        <v>0.017122800000000056</v>
       </c>
       <c r="X2" s="0">
-        <v>10.81978802119788</v>
+        <v>17.10569430569436</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>0.1103007</v>
+      </c>
+      <c r="Z2" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="3">
@@ -805,10 +841,19 @@
         <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>0.10034179999999999</v>
+        <v>0.01495540000000007</v>
       </c>
       <c r="X3" s="0">
-        <v>10.033176682331767</v>
+        <v>14.94045954045961</v>
+      </c>
+      <c r="Y3" s="0">
+        <v>0.0989955</v>
+      </c>
+      <c r="Z3" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="4">
@@ -879,10 +924,19 @@
         <v>0</v>
       </c>
       <c r="W4" s="0">
-        <v>0.092967599999999998</v>
+        <v>0.014358600000000065</v>
       </c>
       <c r="X4" s="0">
-        <v>9.2958304169583048</v>
+        <v>14.344255744255809</v>
+      </c>
+      <c r="Y4" s="0">
+        <v>0.092902899999999997</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="5">
@@ -951,10 +1005,19 @@
         <v>0</v>
       </c>
       <c r="W5" s="0">
-        <v>0.093419600000000005</v>
+        <v>0.014270800000000066</v>
       </c>
       <c r="X5" s="0">
-        <v>9.34102589741026</v>
+        <v>14.256543456543522</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>0.092138300000000006</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="6">
@@ -1025,10 +1088,19 @@
         <v>0</v>
       </c>
       <c r="W6" s="0">
-        <v>0.091662300000000002</v>
+        <v>0.014598400000000069</v>
       </c>
       <c r="X6" s="0">
-        <v>9.1653134686531352</v>
+        <v>14.583816183816253</v>
+      </c>
+      <c r="Y6" s="0">
+        <v>0.093390100000000004</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -1099,10 +1171,19 @@
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>0.091236200000000003</v>
+        <v>0.013959000000000107</v>
       </c>
       <c r="X7" s="0">
-        <v>9.1227077292270771</v>
+        <v>13.945054945055052</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>0.090975100000000003</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="8">
@@ -1173,10 +1254,19 @@
         <v>0</v>
       </c>
       <c r="W8" s="0">
-        <v>0.089968099999999995</v>
+        <v>0.014020600000000091</v>
       </c>
       <c r="X8" s="0">
-        <v>8.9959104089591033</v>
+        <v>14.006593406593497</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>0.090772000000000005</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="9">
@@ -1247,10 +1337,19 @@
         <v>10</v>
       </c>
       <c r="W9" s="0">
-        <v>0.090947399999999998</v>
+        <v>0.013735700000000094</v>
       </c>
       <c r="X9" s="0">
-        <v>9.0938306169383054</v>
+        <v>13.721978021978117</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>0.0898809</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="10">
@@ -1321,10 +1420,19 @@
         <v>10</v>
       </c>
       <c r="W10" s="0">
-        <v>0.090223800000000007</v>
+        <v>0.013935600000000126</v>
       </c>
       <c r="X10" s="0">
-        <v>9.0214778522147778</v>
+        <v>13.921678321678447</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>0.091089500000000004</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="11">
@@ -1395,10 +1503,19 @@
         <v>10</v>
       </c>
       <c r="W11" s="0">
-        <v>0.089454099999999995</v>
+        <v>0.014477900000000142</v>
       </c>
       <c r="X11" s="0">
-        <v>8.9445155484451551</v>
+        <v>14.463436563436705</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>0.091667700000000005</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="12">
@@ -1469,10 +1586,19 @@
         <v>10</v>
       </c>
       <c r="W12" s="0">
-        <v>0.089001800000000006</v>
+        <v>0.014718000000000068</v>
       </c>
       <c r="X12" s="0">
-        <v>8.899290070992901</v>
+        <v>14.703296703296772</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>0.092750899999999997</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="13">
@@ -1543,10 +1669,19 @@
         <v>0</v>
       </c>
       <c r="W13" s="0">
-        <v>0.091033199999999995</v>
+        <v>0.013794300000000094</v>
       </c>
       <c r="X13" s="0">
-        <v>9.1024097590240967</v>
+        <v>13.780519480519574</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>0.090725799999999995</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="14">
@@ -1615,10 +1750,19 @@
         <v>0</v>
       </c>
       <c r="W14" s="0">
-        <v>0.1014462</v>
+        <v>0.020527200000000138</v>
       </c>
       <c r="X14" s="0">
-        <v>10.143605639436057</v>
+        <v>20.506693306693446</v>
+      </c>
+      <c r="Y14" s="0">
+        <v>0.0993473</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="15">
@@ -1687,10 +1831,19 @@
         <v>0</v>
       </c>
       <c r="W15" s="0">
-        <v>0.095699900000000004</v>
+        <v>0.019515500000000151</v>
       </c>
       <c r="X15" s="0">
-        <v>9.5690330966903314</v>
+        <v>19.496003996004148</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>0.097624799999999998</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="16">
@@ -1759,10 +1912,19 @@
         <v>0</v>
       </c>
       <c r="W16" s="0">
-        <v>0.098505800000000004</v>
+        <v>0.020897800000000147</v>
       </c>
       <c r="X16" s="0">
-        <v>9.8495950404959523</v>
+        <v>20.876923076923223</v>
+      </c>
+      <c r="Y16" s="0">
+        <v>0.1011372</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="17">
@@ -1831,10 +1993,19 @@
         <v>0</v>
       </c>
       <c r="W17" s="0">
-        <v>0.096547599999999997</v>
+        <v>0.020596200000000207</v>
       </c>
       <c r="X17" s="0">
-        <v>9.6537946205379459</v>
+        <v>20.575624375624582</v>
+      </c>
+      <c r="Y17" s="0">
+        <v>0.099673200000000003</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="18">
@@ -1903,10 +2074,19 @@
         <v>0</v>
       </c>
       <c r="W18" s="0">
-        <v>0.1002788</v>
+        <v>0.020417200000000094</v>
       </c>
       <c r="X18" s="0">
-        <v>10.026877312268773</v>
+        <v>20.39680319680329</v>
+      </c>
+      <c r="Y18" s="0">
+        <v>0.099572400000000005</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="19">
@@ -1975,10 +2155,19 @@
         <v>0</v>
       </c>
       <c r="W19" s="0">
-        <v>0.1048557</v>
+        <v>0.02050430000000025</v>
       </c>
       <c r="X19" s="0">
-        <v>10.484521547845215</v>
+        <v>20.483816183816433</v>
+      </c>
+      <c r="Y19" s="0">
+        <v>0.099601999999999996</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="20">
@@ -2047,10 +2236,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="0">
-        <v>0.10085760000000001</v>
+        <v>0.02206060000000026</v>
       </c>
       <c r="X20" s="0">
-        <v>10.084751524847515</v>
+        <v>22.0385614385617</v>
+      </c>
+      <c r="Y20" s="0">
+        <v>0.1035262</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="21">
@@ -2119,10 +2317,19 @@
         <v>1.2230000000000003</v>
       </c>
       <c r="W21" s="0">
-        <v>0.099269399999999994</v>
+        <v>0.020489700000000149</v>
       </c>
       <c r="X21" s="0">
-        <v>9.9259474052594747</v>
+        <v>20.469230769230919</v>
+      </c>
+      <c r="Y21" s="0">
+        <v>0.099656400000000006</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="22">
@@ -2191,10 +2398,19 @@
         <v>0</v>
       </c>
       <c r="W22" s="0">
-        <v>0.098639500000000005</v>
+        <v>0.020285500000000147</v>
       </c>
       <c r="X22" s="0">
-        <v>9.8629637036296387</v>
+        <v>20.265234765234912</v>
+      </c>
+      <c r="Y22" s="0">
+        <v>0.099322099999999997</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="23">
@@ -2263,10 +2479,19 @@
         <v>0</v>
       </c>
       <c r="W23" s="0">
-        <v>0.099732000000000001</v>
+        <v>0.021188200000000115</v>
       </c>
       <c r="X23" s="0">
-        <v>9.9722027797220285</v>
+        <v>21.16703296703308</v>
+      </c>
+      <c r="Y23" s="0">
+        <v>0.1014376</v>
+      </c>
+      <c r="Z23" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="24">
@@ -2335,10 +2560,19 @@
         <v>1.2569999999999997</v>
       </c>
       <c r="W24" s="0">
-        <v>0.095940800000000007</v>
+        <v>0.020928600000000203</v>
       </c>
       <c r="X24" s="0">
-        <v>9.5931206879312079</v>
+        <v>20.907692307692511</v>
+      </c>
+      <c r="Y24" s="0">
+        <v>0.1006842</v>
+      </c>
+      <c r="Z24" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="25">
@@ -2407,10 +2641,19 @@
         <v>0</v>
       </c>
       <c r="W25" s="0">
-        <v>0.1007156</v>
+        <v>0.019917900000000141</v>
       </c>
       <c r="X25" s="0">
-        <v>10.070552944705529</v>
+        <v>19.898001998002137</v>
+      </c>
+      <c r="Y25" s="0">
+        <v>0.098455899999999999</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="26">
@@ -2479,10 +2722,19 @@
         <v>0</v>
       </c>
       <c r="W26" s="0">
-        <v>0.1583196</v>
+        <v>0.073372400000000088</v>
       </c>
       <c r="X26" s="0">
-        <v>15.830376962303772</v>
+        <v>73.299100899100978</v>
+      </c>
+      <c r="Y26" s="0">
+        <v>0.1633144</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="27">
@@ -2551,10 +2803,19 @@
         <v>0</v>
       </c>
       <c r="W27" s="0">
-        <v>0.1468863</v>
+        <v>0.064758200000000002</v>
       </c>
       <c r="X27" s="0">
-        <v>14.687161283871612</v>
+        <v>64.69350649350649</v>
+      </c>
+      <c r="Y27" s="0">
+        <v>0.15135680000000001</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="28">
@@ -2623,10 +2884,19 @@
         <v>0</v>
       </c>
       <c r="W28" s="0">
-        <v>0.14427190000000001</v>
+        <v>0.060318899999999759</v>
       </c>
       <c r="X28" s="0">
-        <v>14.425747425257475</v>
+        <v>60.258641358641121</v>
+      </c>
+      <c r="Y28" s="0">
+        <v>0.14545079999999999</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="29">
@@ -2695,10 +2965,19 @@
         <v>0</v>
       </c>
       <c r="W29" s="0">
-        <v>0.14087540000000001</v>
+        <v>0.059431999999999985</v>
       </c>
       <c r="X29" s="0">
-        <v>14.086131386861315</v>
+        <v>59.372627372627356</v>
+      </c>
+      <c r="Y29" s="0">
+        <v>0.14363409999999999</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="30">
@@ -2767,10 +3046,19 @@
         <v>0</v>
       </c>
       <c r="W30" s="0">
-        <v>0.14723800000000001</v>
+        <v>0.061050399999999928</v>
       </c>
       <c r="X30" s="0">
-        <v>14.722327767223279</v>
+        <v>60.989410589410518</v>
+      </c>
+      <c r="Y30" s="0">
+        <v>0.1468796</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="31">
@@ -2839,10 +3127,19 @@
         <v>0</v>
       </c>
       <c r="W31" s="0">
-        <v>0.1457977</v>
+        <v>0.061137899999999967</v>
       </c>
       <c r="X31" s="0">
-        <v>14.578312168783123</v>
+        <v>61.07682317682314</v>
+      </c>
+      <c r="Y31" s="0">
+        <v>0.1463585</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="32">
@@ -2911,10 +3208,19 @@
         <v>0</v>
       </c>
       <c r="W32" s="0">
-        <v>0.1467049</v>
+        <v>0.070177500000000143</v>
       </c>
       <c r="X32" s="0">
-        <v>14.66902309769023</v>
+        <v>70.107392607392754</v>
+      </c>
+      <c r="Y32" s="0">
+        <v>0.1612035</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="33">
@@ -2983,10 +3289,19 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="W33" s="0">
-        <v>0.14320569999999999</v>
+        <v>0.059844899999999875</v>
       </c>
       <c r="X33" s="0">
-        <v>14.31913808619138</v>
+        <v>59.785114885114759</v>
+      </c>
+      <c r="Y33" s="0">
+        <v>0.14456769999999999</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="34">
@@ -3055,10 +3370,19 @@
         <v>0</v>
       </c>
       <c r="W34" s="0">
-        <v>0.1436201</v>
+        <v>0.061668499999999932</v>
       </c>
       <c r="X34" s="0">
-        <v>14.36057394260574</v>
+        <v>61.60689310689304</v>
+      </c>
+      <c r="Y34" s="0">
+        <v>0.14778089999999999</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="35">
@@ -3127,10 +3451,19 @@
         <v>0</v>
       </c>
       <c r="W35" s="0">
-        <v>0.14593249999999999</v>
+        <v>0.060563899999999817</v>
       </c>
       <c r="X35" s="0">
-        <v>14.591790820917907</v>
+        <v>60.503396603396418</v>
+      </c>
+      <c r="Y35" s="0">
+        <v>0.14660670000000001</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="36">
@@ -3199,10 +3532,19 @@
         <v>1.3010000000000002</v>
       </c>
       <c r="W36" s="0">
-        <v>0.14628169999999999</v>
+        <v>0.058736900000000092</v>
       </c>
       <c r="X36" s="0">
-        <v>14.626707329267072</v>
+        <v>58.678221778221868</v>
+      </c>
+      <c r="Y36" s="0">
+        <v>0.14325109999999999</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="37">
@@ -3271,10 +3613,19 @@
         <v>0</v>
       </c>
       <c r="W37" s="0">
-        <v>0.14229049999999999</v>
+        <v>0.059703499999999979</v>
       </c>
       <c r="X37" s="0">
-        <v>14.227627237276272</v>
+        <v>59.643856143856127</v>
+      </c>
+      <c r="Y37" s="0">
+        <v>0.1463796</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="38">
@@ -3343,10 +3694,19 @@
         <v>0</v>
       </c>
       <c r="W38" s="0">
-        <v>0.1137904</v>
+        <v>0.013337099999999978</v>
       </c>
       <c r="X38" s="0">
-        <v>11.377902209779023</v>
+        <v>13.323776223776202</v>
+      </c>
+      <c r="Y38" s="0">
+        <v>0.1128861</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="39">
@@ -3415,10 +3775,19 @@
         <v>0</v>
       </c>
       <c r="W39" s="0">
-        <v>0.092916499999999999</v>
+        <v>0.013053099999999989</v>
       </c>
       <c r="X39" s="0">
-        <v>9.2907209279072092</v>
+        <v>13.04005994005993</v>
+      </c>
+      <c r="Y39" s="0">
+        <v>0.093360499999999999</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="40">
@@ -3487,10 +3856,19 @@
         <v>0</v>
       </c>
       <c r="W40" s="0">
-        <v>0.089454199999999998</v>
+        <v>0.012492700000000009</v>
       </c>
       <c r="X40" s="0">
-        <v>8.9445255474452541</v>
+        <v>12.480219780219789</v>
+      </c>
+      <c r="Y40" s="0">
+        <v>0.091762700000000003</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="41">
@@ -3559,10 +3937,19 @@
         <v>0</v>
       </c>
       <c r="W41" s="0">
-        <v>0.090125800000000006</v>
+        <v>0.01242220000000001</v>
       </c>
       <c r="X41" s="0">
-        <v>9.0116788321167896</v>
+        <v>12.40979020979022</v>
+      </c>
+      <c r="Y41" s="0">
+        <v>0.0907385</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="42">
@@ -3631,10 +4018,19 @@
         <v>0</v>
       </c>
       <c r="W42" s="0">
-        <v>0.088824799999999996</v>
+        <v>0.012763100000000008</v>
       </c>
       <c r="X42" s="0">
-        <v>8.8815918408159185</v>
+        <v>12.750349650349659</v>
+      </c>
+      <c r="Y42" s="0">
+        <v>0.091917499999999999</v>
+      </c>
+      <c r="Z42" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="43">
@@ -3703,10 +4099,19 @@
         <v>0</v>
       </c>
       <c r="W43" s="0">
-        <v>0.090095599999999998</v>
+        <v>0.012712800000000007</v>
       </c>
       <c r="X43" s="0">
-        <v>9.0086591340865905</v>
+        <v>12.700099900099907</v>
+      </c>
+      <c r="Y43" s="0">
+        <v>0.091662099999999996</v>
+      </c>
+      <c r="Z43" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="44">
@@ -3775,10 +4180,19 @@
         <v>0</v>
       </c>
       <c r="W44" s="0">
-        <v>0.091754299999999997</v>
+        <v>0.012489000000000019</v>
       </c>
       <c r="X44" s="0">
-        <v>9.1745125487451258</v>
+        <v>12.476523476523495</v>
+      </c>
+      <c r="Y44" s="0">
+        <v>0.091021500000000005</v>
+      </c>
+      <c r="Z44" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="45">
@@ -3847,10 +4261,19 @@
         <v>1.7040000000000002</v>
       </c>
       <c r="W45" s="0">
-        <v>0.090112100000000001</v>
+        <v>0.012594900000000004</v>
       </c>
       <c r="X45" s="0">
-        <v>9.0103089691030895</v>
+        <v>12.582317682317687</v>
+      </c>
+      <c r="Y45" s="0">
+        <v>0.091761999999999996</v>
+      </c>
+      <c r="Z45" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="46">
@@ -3919,10 +4342,19 @@
         <v>0</v>
       </c>
       <c r="W46" s="0">
-        <v>0.087913099999999994</v>
+        <v>0.012937400000000043</v>
       </c>
       <c r="X46" s="0">
-        <v>8.7904309569043075</v>
+        <v>12.924475524475568</v>
+      </c>
+      <c r="Y46" s="0">
+        <v>0.092540999999999998</v>
+      </c>
+      <c r="Z46" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="47">
@@ -3991,10 +4423,19 @@
         <v>0</v>
       </c>
       <c r="W47" s="0">
-        <v>0.087537100000000007</v>
+        <v>0.012015099999999996</v>
       </c>
       <c r="X47" s="0">
-        <v>8.7528347165283478</v>
+        <v>12.003096903096898</v>
+      </c>
+      <c r="Y47" s="0">
+        <v>0.090044899999999997</v>
+      </c>
+      <c r="Z47" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="48">
@@ -4063,10 +4504,19 @@
         <v>2.3819999999999997</v>
       </c>
       <c r="W48" s="0">
-        <v>0.088836700000000005</v>
+        <v>0.012704499999999985</v>
       </c>
       <c r="X48" s="0">
-        <v>8.8827817218278167</v>
+        <v>12.691808191808176</v>
+      </c>
+      <c r="Y48" s="0">
+        <v>0.092234499999999997</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="49">
@@ -4135,10 +4585,19 @@
         <v>0</v>
       </c>
       <c r="W49" s="0">
-        <v>0.089467699999999997</v>
+        <v>0.011943499999999992</v>
       </c>
       <c r="X49" s="0">
-        <v>8.9458754124587543</v>
+        <v>11.931568431568424</v>
+      </c>
+      <c r="Y49" s="0">
+        <v>0.089705999999999994</v>
+      </c>
+      <c r="Z49" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA49" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="50">
@@ -4207,10 +4666,19 @@
         <v>0</v>
       </c>
       <c r="W50" s="0">
-        <v>0.1126921</v>
+        <v>0.03146520000000004</v>
       </c>
       <c r="X50" s="0">
-        <v>11.268083191680832</v>
+        <v>31.433766233766271</v>
+      </c>
+      <c r="Y50" s="0">
+        <v>0.1153718</v>
+      </c>
+      <c r="Z50" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA50" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="51">
@@ -4279,10 +4747,19 @@
         <v>0</v>
       </c>
       <c r="W51" s="0">
-        <v>0.11072410000000001</v>
+        <v>0.029196900000000039</v>
       </c>
       <c r="X51" s="0">
-        <v>11.07130286971303</v>
+        <v>29.167732267732308</v>
+      </c>
+      <c r="Y51" s="0">
+        <v>0.1106369</v>
+      </c>
+      <c r="Z51" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA51" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="52">
@@ -4351,10 +4828,19 @@
         <v>0</v>
       </c>
       <c r="W52" s="0">
-        <v>0.1086867</v>
+        <v>0.028402099999999965</v>
       </c>
       <c r="X52" s="0">
-        <v>10.867583241675833</v>
+        <v>28.373726273726238</v>
+      </c>
+      <c r="Y52" s="0">
+        <v>0.10975409999999999</v>
+      </c>
+      <c r="Z52" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA52" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4909,19 @@
         <v>0</v>
       </c>
       <c r="W53" s="0">
-        <v>0.1092482</v>
+        <v>0.028905800000000002</v>
       </c>
       <c r="X53" s="0">
-        <v>10.923727627237277</v>
+        <v>28.876923076923077</v>
+      </c>
+      <c r="Y53" s="0">
+        <v>0.1109087</v>
+      </c>
+      <c r="Z53" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA53" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="54">
@@ -4495,10 +4990,19 @@
         <v>0</v>
       </c>
       <c r="W54" s="0">
-        <v>0.10791050000000001</v>
+        <v>0.028324399999999996</v>
       </c>
       <c r="X54" s="0">
-        <v>10.789971002899712</v>
+        <v>28.296103896103894</v>
+      </c>
+      <c r="Y54" s="0">
+        <v>0.11013539999999999</v>
+      </c>
+      <c r="Z54" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA54" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="55">
@@ -4567,10 +5071,19 @@
         <v>0</v>
       </c>
       <c r="W55" s="0">
-        <v>0.1072222</v>
+        <v>0.027825600000000061</v>
       </c>
       <c r="X55" s="0">
-        <v>10.721147885211478</v>
+        <v>27.797802197802259</v>
+      </c>
+      <c r="Y55" s="0">
+        <v>0.10945249999999999</v>
+      </c>
+      <c r="Z55" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA55" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="56">
@@ -4639,10 +5152,19 @@
         <v>0</v>
       </c>
       <c r="W56" s="0">
-        <v>0.1055241</v>
+        <v>0.028293199999999994</v>
       </c>
       <c r="X56" s="0">
-        <v>10.551354864513549</v>
+        <v>28.264935064935059</v>
+      </c>
+      <c r="Y56" s="0">
+        <v>0.10979510000000001</v>
+      </c>
+      <c r="Z56" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA56" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="57">
@@ -4711,10 +5233,19 @@
         <v>1.6260000000000003</v>
       </c>
       <c r="W57" s="0">
-        <v>0.1084354</v>
+        <v>0.028266600000000013</v>
       </c>
       <c r="X57" s="0">
-        <v>10.842455754424558</v>
+        <v>28.238361638361653</v>
+      </c>
+      <c r="Y57" s="0">
+        <v>0.10962470000000001</v>
+      </c>
+      <c r="Z57" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA57" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="58">
@@ -4783,10 +5314,19 @@
         <v>0</v>
       </c>
       <c r="W58" s="0">
-        <v>0.10818759999999999</v>
+        <v>0.029013699999999979</v>
       </c>
       <c r="X58" s="0">
-        <v>10.817678232176782</v>
+        <v>28.984715284715264</v>
+      </c>
+      <c r="Y58" s="0">
+        <v>0.1111404</v>
+      </c>
+      <c r="Z58" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA58" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="59">
@@ -4855,10 +5395,19 @@
         <v>0</v>
       </c>
       <c r="W59" s="0">
-        <v>0.1069399</v>
+        <v>0.028494699999999967</v>
       </c>
       <c r="X59" s="0">
-        <v>10.692920707929208</v>
+        <v>28.466233766233731</v>
+      </c>
+      <c r="Y59" s="0">
+        <v>0.1097265</v>
+      </c>
+      <c r="Z59" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA59" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="60">
@@ -4927,10 +5476,19 @@
         <v>0.3879999999999999</v>
       </c>
       <c r="W60" s="0">
-        <v>0.1101475</v>
+        <v>0.032519700000000082</v>
       </c>
       <c r="X60" s="0">
-        <v>11.013648635136486</v>
+        <v>32.487212787212869</v>
+      </c>
+      <c r="Y60" s="0">
+        <v>0.119492</v>
+      </c>
+      <c r="Z60" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA60" s="0">
+        <v>1001</v>
       </c>
     </row>
     <row r="61">
@@ -4999,10 +5557,19 @@
         <v>0</v>
       </c>
       <c r="W61" s="0">
-        <v>0.10971450000000001</v>
+        <v>0.03315499999999999</v>
       </c>
       <c r="X61" s="0">
-        <v>10.97035296470353</v>
+        <v>33.121878121878112</v>
+      </c>
+      <c r="Y61" s="0">
+        <v>0.12115620000000001</v>
+      </c>
+      <c r="Z61" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA61" s="0">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -5027,7 +5594,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -5038,7 +5605,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -5049,7 +5616,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -5060,7 +5627,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -5071,7 +5638,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -5082,7 +5649,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -5093,7 +5660,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -5104,7 +5671,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -5115,7 +5682,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -5126,7 +5693,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -5137,7 +5704,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -5148,7 +5715,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
@@ -5159,7 +5726,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -5170,7 +5737,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -5181,7 +5748,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5192,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -5203,7 +5770,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -5214,7 +5781,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
@@ -5225,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -5236,7 +5803,7 @@
         <v>13</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
@@ -5247,7 +5814,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
@@ -5258,7 +5825,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
@@ -5269,7 +5836,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
@@ -5280,7 +5847,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
@@ -5291,7 +5858,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
@@ -5302,7 +5869,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27">
@@ -5313,7 +5880,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
@@ -5324,7 +5891,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
@@ -5335,7 +5902,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
@@ -5346,7 +5913,7 @@
         <v>11</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
@@ -5357,7 +5924,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
@@ -5368,7 +5935,7 @@
         <v>13</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33">
@@ -5379,7 +5946,7 @@
         <v>14</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34">
@@ -5390,7 +5957,7 @@
         <v>15</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35">
@@ -5401,7 +5968,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
@@ -5412,7 +5979,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
@@ -5423,7 +5990,7 @@
         <v>18</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
@@ -5434,7 +6001,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39">
@@ -5445,7 +6012,7 @@
         <v>8</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40">
@@ -5456,7 +6023,7 @@
         <v>9</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41">
@@ -5467,7 +6034,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
@@ -5478,7 +6045,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43">
@@ -5489,7 +6056,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44">
@@ -5500,7 +6067,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45">
@@ -5511,7 +6078,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
@@ -5522,7 +6089,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47">
@@ -5533,7 +6100,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
@@ -5544,7 +6111,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49">
@@ -5555,7 +6122,7 @@
         <v>18</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50">
@@ -5566,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51">
@@ -5577,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
@@ -5588,7 +6155,7 @@
         <v>9</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53">
@@ -5599,7 +6166,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54">
@@ -5610,7 +6177,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55">
@@ -5621,7 +6188,7 @@
         <v>12</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
@@ -5632,7 +6199,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57">
@@ -5643,7 +6210,7 @@
         <v>14</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -5654,7 +6221,7 @@
         <v>15</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59">
@@ -5665,7 +6232,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60">
@@ -5676,7 +6243,7 @@
         <v>17</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61">
@@ -5687,7 +6254,7 @@
         <v>18</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -5701,15 +6268,15 @@
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
     <col min="2" max="2" width="25.000000" customWidth="true"/>
-    <col min="3" max="3" width="21.08984375" customWidth="true"/>
-    <col min="4" max="4" width="24.26953125" customWidth="true"/>
-    <col min="5" max="5" width="26.453125" customWidth="true"/>
-    <col min="6" max="6" width="15.90625" customWidth="true"/>
-    <col min="7" max="7" width="19.08984375" customWidth="true"/>
-    <col min="8" max="8" width="14.08984375" customWidth="true"/>
-    <col min="9" max="9" width="26.6328125" customWidth="true"/>
-    <col min="10" max="10" width="18.08984375" customWidth="true"/>
-    <col min="11" max="11" width="8.36328125" customWidth="true"/>
+    <col min="3" max="3" width="27.000000" customWidth="true"/>
+    <col min="4" max="4" width="29.000000" customWidth="true"/>
+    <col min="5" max="5" width="32.000000" customWidth="true"/>
+    <col min="6" max="6" width="22.000000" customWidth="true"/>
+    <col min="7" max="7" width="24.000000" customWidth="true"/>
+    <col min="8" max="8" width="19.000000" customWidth="true"/>
+    <col min="9" max="9" width="33.000000" customWidth="true"/>
+    <col min="10" max="10" width="23.000000" customWidth="true"/>
+    <col min="11" max="11" width="12.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5720,31 +6287,31 @@
         <v>6</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -5752,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C2" s="0">
         <v>4.9261314660201569e-05</v>
@@ -5785,7 +6352,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C3" s="0">
         <v>1.0778502246144676e-10</v>
@@ -5818,7 +6385,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C4" s="0">
         <v>3.4830572372175117e-10</v>
@@ -5853,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C5" s="0">
         <v>4.8896654964814556e-11</v>
@@ -5886,7 +6453,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C6" s="0">
         <v>1.9074581563407075e-11</v>
@@ -5925,19 +6492,19 @@
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
     <col min="2" max="2" width="20.000000" customWidth="true"/>
-    <col min="3" max="3" width="2.90625" customWidth="true"/>
+    <col min="3" max="3" width="12.000000" customWidth="true"/>
     <col min="4" max="4" width="14.453125" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
     <col min="6" max="6" width="14.453125" customWidth="true"/>
     <col min="7" max="7" width="14.453125" customWidth="true"/>
     <col min="8" max="8" width="14.453125" customWidth="true"/>
-    <col min="9" max="9" width="15.36328125" customWidth="true"/>
-    <col min="10" max="10" width="15.90625" customWidth="true"/>
-    <col min="11" max="11" width="6.81640625" customWidth="true"/>
-    <col min="12" max="12" width="12.81640625" customWidth="true"/>
-    <col min="13" max="13" width="11.453125" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="13.90625" customWidth="true"/>
+    <col min="9" max="9" width="20.000000" customWidth="true"/>
+    <col min="10" max="10" width="21.000000" customWidth="true"/>
+    <col min="11" max="11" width="12.000000" customWidth="true"/>
+    <col min="12" max="12" width="17.000000" customWidth="true"/>
+    <col min="13" max="13" width="16.000000" customWidth="true"/>
+    <col min="14" max="14" width="18.000000" customWidth="true"/>
+    <col min="15" max="15" width="19.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5945,46 +6512,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -6853,45 +7420,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
     <col min="2" max="2" width="18.000000" customWidth="true"/>
     <col min="3" max="3" width="12.000000" customWidth="true"/>
-    <col min="4" max="4" width="4.90625" customWidth="true"/>
-    <col min="5" max="5" width="7.08984375" customWidth="true"/>
-    <col min="6" max="6" width="16.81640625" customWidth="true"/>
+    <col min="4" max="4" width="12.000000" customWidth="true"/>
+    <col min="5" max="5" width="12.000000" customWidth="true"/>
+    <col min="6" max="6" width="22.000000" customWidth="true"/>
     <col min="7" max="7" width="20.000000" customWidth="true"/>
-    <col min="8" max="8" width="12.6328125" customWidth="true"/>
-    <col min="9" max="9" width="13.453125" customWidth="true"/>
-    <col min="10" max="10" width="17.7265625" customWidth="true"/>
-    <col min="11" max="11" width="17.54296875" customWidth="true"/>
-    <col min="12" max="12" width="12.453125" customWidth="true"/>
-    <col min="13" max="13" width="19.1796875" customWidth="true"/>
-    <col min="14" max="14" width="12.453125" customWidth="true"/>
-    <col min="15" max="15" width="21.453125" customWidth="true"/>
-    <col min="16" max="16" width="19.36328125" customWidth="true"/>
-    <col min="17" max="17" width="17.08984375" customWidth="true"/>
-    <col min="18" max="18" width="13.453125" customWidth="true"/>
-    <col min="19" max="19" width="13.453125" customWidth="true"/>
-    <col min="20" max="20" width="14.1796875" customWidth="true"/>
-    <col min="21" max="21" width="14.36328125" customWidth="true"/>
-    <col min="22" max="22" width="23.6328125" customWidth="true"/>
-    <col min="23" max="23" width="24.36328125" customWidth="true"/>
-    <col min="24" max="24" width="20.7265625" customWidth="true"/>
-    <col min="25" max="25" width="9.36328125" customWidth="true"/>
-    <col min="26" max="26" width="3.81640625" customWidth="true"/>
-    <col min="27" max="27" width="15.54296875" customWidth="true"/>
-    <col min="28" max="28" width="15.81640625" customWidth="true"/>
-    <col min="29" max="29" width="16.6328125" customWidth="true"/>
-    <col min="30" max="30" width="14.81640625" customWidth="true"/>
-    <col min="31" max="31" width="18.36328125" customWidth="true"/>
-    <col min="32" max="32" width="14.6328125" customWidth="true"/>
-    <col min="33" max="33" width="11.453125" customWidth="true"/>
-    <col min="34" max="34" width="13.36328125" customWidth="true"/>
-    <col min="35" max="35" width="14.08984375" customWidth="true"/>
-    <col min="36" max="36" width="22.90625" customWidth="true"/>
+    <col min="8" max="8" width="17.000000" customWidth="true"/>
+    <col min="9" max="9" width="17.000000" customWidth="true"/>
+    <col min="10" max="10" width="21.000000" customWidth="true"/>
+    <col min="11" max="11" width="21.000000" customWidth="true"/>
+    <col min="12" max="12" width="14.000000" customWidth="true"/>
+    <col min="13" max="13" width="26.000000" customWidth="true"/>
+    <col min="14" max="14" width="17.000000" customWidth="true"/>
+    <col min="15" max="15" width="28.000000" customWidth="true"/>
+    <col min="16" max="16" width="26.000000" customWidth="true"/>
+    <col min="17" max="17" width="22.000000" customWidth="true"/>
+    <col min="18" max="18" width="18.000000" customWidth="true"/>
+    <col min="19" max="19" width="18.000000" customWidth="true"/>
+    <col min="20" max="20" width="19.000000" customWidth="true"/>
+    <col min="21" max="21" width="20.000000" customWidth="true"/>
+    <col min="22" max="22" width="29.000000" customWidth="true"/>
+    <col min="23" max="23" width="30.000000" customWidth="true"/>
+    <col min="24" max="24" width="24.000000" customWidth="true"/>
+    <col min="25" max="25" width="30.000000" customWidth="true"/>
+    <col min="26" max="26" width="31.000000" customWidth="true"/>
+    <col min="27" max="27" width="30.000000" customWidth="true"/>
+    <col min="28" max="28" width="13.000000" customWidth="true"/>
+    <col min="29" max="29" width="12.000000" customWidth="true"/>
+    <col min="30" max="30" width="19.000000" customWidth="true"/>
+    <col min="31" max="31" width="20.000000" customWidth="true"/>
+    <col min="32" max="32" width="22.000000" customWidth="true"/>
+    <col min="33" max="33" width="21.000000" customWidth="true"/>
+    <col min="34" max="34" width="23.000000" customWidth="true"/>
+    <col min="35" max="35" width="19.000000" customWidth="true"/>
+    <col min="36" max="36" width="15.000000" customWidth="true"/>
+    <col min="37" max="37" width="18.000000" customWidth="true"/>
+    <col min="38" max="38" width="18.000000" customWidth="true"/>
+    <col min="39" max="39" width="26.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6968,13 +7538,13 @@
         <v>42</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="Z1" s="0" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA1" s="0" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AB1" s="0" t="s">
         <v>61</v>
@@ -7003,13 +7573,22 @@
       <c r="AJ1" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="AK1" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL1" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="AM1" s="0" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>20</v>
@@ -7072,45 +7651,54 @@
         <v>10</v>
       </c>
       <c r="W2" s="0">
-        <v>0.12622549999999999</v>
+        <v>0.018683600000000078</v>
       </c>
       <c r="X2" s="0">
-        <v>12.621287871212878</v>
+        <v>18.664935064935143</v>
       </c>
       <c r="Y2" s="0">
-        <v>0</v>
+        <v>0.11869010000000001</v>
       </c>
       <c r="Z2" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA2" s="0">
+      <c r="AD2" s="0">
         <v>-0.056130873014615418</v>
       </c>
-      <c r="AB2" s="0">
+      <c r="AE2" s="0">
         <v>-0.017397652624266555</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AF2" s="0">
         <v>0.095327095632060238</v>
       </c>
-      <c r="AD2" s="0">
+      <c r="AG2" s="0">
         <v>2.5333941298887757</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AH2" s="0">
         <v>0.60946739476013612</v>
       </c>
-      <c r="AF2" s="0">
+      <c r="AI2" s="0">
         <v>8.9377524711883503</v>
       </c>
-      <c r="AG2" s="0">
+      <c r="AJ2" s="0">
         <v>3.3962821780378363</v>
       </c>
-      <c r="AH2" s="0">
+      <c r="AK2" s="0">
         <v>0.28234303636905489</v>
       </c>
-      <c r="AI2" s="0">
+      <c r="AL2" s="0">
         <v>0.058250114865858293</v>
       </c>
-      <c r="AJ2" s="0">
+      <c r="AM2" s="0">
         <v>2026</v>
       </c>
     </row>
@@ -7119,7 +7707,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>20</v>
@@ -7180,45 +7768,54 @@
         <v>0.00037478559310910598</v>
       </c>
       <c r="W3" s="0">
-        <v>0.1113161</v>
+        <v>0.022153800000000102</v>
       </c>
       <c r="X3" s="0">
-        <v>11.13049695030497</v>
+        <v>22.131668331668436</v>
       </c>
       <c r="Y3" s="0">
-        <v>0</v>
+        <v>0.1051614</v>
       </c>
       <c r="Z3" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA3" s="0">
+      <c r="AD3" s="0">
         <v>-0.056130873014615418</v>
       </c>
-      <c r="AB3" s="0">
+      <c r="AE3" s="0">
         <v>-0.017397652624266555</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AF3" s="0">
         <v>0.095327095632060238</v>
       </c>
-      <c r="AD3" s="0">
+      <c r="AG3" s="0">
         <v>2.5333941298887757</v>
       </c>
-      <c r="AE3" s="0">
+      <c r="AH3" s="0">
         <v>0.60946739476013612</v>
       </c>
-      <c r="AF3" s="0">
+      <c r="AI3" s="0">
         <v>8.9377524711883503</v>
       </c>
-      <c r="AG3" s="0">
+      <c r="AJ3" s="0">
         <v>3.3962821780378363</v>
       </c>
-      <c r="AH3" s="0">
+      <c r="AK3" s="0">
         <v>0.28234303636905489</v>
       </c>
-      <c r="AI3" s="0">
+      <c r="AL3" s="0">
         <v>0.058250114865858293</v>
       </c>
-      <c r="AJ3" s="0">
+      <c r="AM3" s="0">
         <v>2026</v>
       </c>
     </row>
@@ -7227,7 +7824,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>20</v>
@@ -7288,45 +7885,54 @@
         <v>0.00037478559310910598</v>
       </c>
       <c r="W4" s="0">
-        <v>0.16273080000000001</v>
+        <v>0.072221900000000103</v>
       </c>
       <c r="X4" s="0">
-        <v>16.271452854714529</v>
+        <v>72.149750249750355</v>
       </c>
       <c r="Y4" s="0">
-        <v>0</v>
+        <v>0.16264300000000001</v>
       </c>
       <c r="Z4" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA4" s="0">
+      <c r="AD4" s="0">
         <v>-0.056130873014615418</v>
       </c>
-      <c r="AB4" s="0">
+      <c r="AE4" s="0">
         <v>-0.017397652624266555</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AF4" s="0">
         <v>0.095327095632060238</v>
       </c>
-      <c r="AD4" s="0">
+      <c r="AG4" s="0">
         <v>2.5333941298887757</v>
       </c>
-      <c r="AE4" s="0">
+      <c r="AH4" s="0">
         <v>0.60946739476013612</v>
       </c>
-      <c r="AF4" s="0">
+      <c r="AI4" s="0">
         <v>8.9377524711883503</v>
       </c>
-      <c r="AG4" s="0">
+      <c r="AJ4" s="0">
         <v>3.3962821780378363</v>
       </c>
-      <c r="AH4" s="0">
+      <c r="AK4" s="0">
         <v>0.28234303636905489</v>
       </c>
-      <c r="AI4" s="0">
+      <c r="AL4" s="0">
         <v>0.058250114865858293</v>
       </c>
-      <c r="AJ4" s="0">
+      <c r="AM4" s="0">
         <v>2026</v>
       </c>
     </row>
@@ -7335,7 +7941,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>20</v>
@@ -7354,37 +7960,37 @@
         <v>10</v>
       </c>
       <c r="I5" s="0">
-        <v>0.79690795525033731</v>
+        <v>0.80346834601930084</v>
       </c>
       <c r="J5" s="0">
-        <v>3.7247261296421805</v>
+        <v>3.7808820334902191</v>
       </c>
       <c r="K5" s="0">
-        <v>0.065008734697321213</v>
+        <v>0.065988840113902839</v>
       </c>
       <c r="L5" s="0">
-        <v>0.17171363456869182</v>
+        <v>0.17243232742411779</v>
       </c>
       <c r="M5" s="0">
-        <v>1.4630000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="N5" s="0">
-        <v>1.858432497892379</v>
+        <v>1.8772803477324269</v>
       </c>
       <c r="O5" s="0">
-        <v>0.00051624771217084753</v>
+        <v>0.0006501698379638432</v>
       </c>
       <c r="P5" s="0">
-        <v>2.8210000000000002</v>
+        <v>2.8490000000000002</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.0010772982116560303</v>
+        <v>0.0010181295063461659</v>
       </c>
       <c r="R5" s="0">
-        <v>0.60895114704796527</v>
+        <v>0.60881722492217227</v>
       </c>
       <c r="S5" s="0">
-        <v>0.5619207283865566</v>
+        <v>0.48030507769605663</v>
       </c>
       <c r="T5" s="0">
         <v>0.079499999999999904</v>
@@ -7396,45 +8002,54 @@
         <v>0.00037478559310910598</v>
       </c>
       <c r="W5" s="0">
-        <v>0.1242601</v>
+        <v>0.014525400000000056</v>
       </c>
       <c r="X5" s="0">
-        <v>12.424767523247676</v>
+        <v>14.510889110889167</v>
       </c>
       <c r="Y5" s="0">
-        <v>0</v>
+        <v>0.1194254</v>
       </c>
       <c r="Z5" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA5" s="0">
+      <c r="AD5" s="0">
         <v>-0.056130873014615418</v>
       </c>
-      <c r="AB5" s="0">
+      <c r="AE5" s="0">
         <v>-0.017397652624266555</v>
       </c>
-      <c r="AC5" s="0">
+      <c r="AF5" s="0">
         <v>0.095327095632060238</v>
       </c>
-      <c r="AD5" s="0">
+      <c r="AG5" s="0">
         <v>2.5333941298887757</v>
       </c>
-      <c r="AE5" s="0">
+      <c r="AH5" s="0">
         <v>0.60946739476013612</v>
       </c>
-      <c r="AF5" s="0">
+      <c r="AI5" s="0">
         <v>8.9377524711883503</v>
       </c>
-      <c r="AG5" s="0">
+      <c r="AJ5" s="0">
         <v>3.3962821780378363</v>
       </c>
-      <c r="AH5" s="0">
+      <c r="AK5" s="0">
         <v>0.28234303636905489</v>
       </c>
-      <c r="AI5" s="0">
+      <c r="AL5" s="0">
         <v>0.058250114865858293</v>
       </c>
-      <c r="AJ5" s="0">
+      <c r="AM5" s="0">
         <v>2026</v>
       </c>
     </row>
@@ -7443,7 +8058,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>20</v>
@@ -7462,87 +8077,96 @@
         <v>10</v>
       </c>
       <c r="I6" s="0">
-        <v>0.95008625852448214</v>
+        <v>0.95286600158781676</v>
       </c>
       <c r="J6" s="0">
-        <v>3.6269786002255739</v>
+        <v>3.6877884893902206</v>
       </c>
       <c r="K6" s="0">
-        <v>0.063302718473311412</v>
+        <v>0.064364051257007324</v>
       </c>
       <c r="L6" s="0">
-        <v>0.2496453893942169</v>
+        <v>0.25824374062336469</v>
       </c>
       <c r="M6" s="0">
-        <v>1.742</v>
+        <v>3.516</v>
       </c>
       <c r="N6" s="0">
-        <v>1.837701004874708</v>
+        <v>1.8240369896123307</v>
       </c>
       <c r="O6" s="0">
-        <v>0.0011139343960011594</v>
+        <v>0.0012071353192513179</v>
       </c>
       <c r="P6" s="0">
-        <v>2.8690000000000002</v>
+        <v>2.8730000000000002</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0032344541239431868</v>
+        <v>0.0034681069831632438</v>
       </c>
       <c r="R6" s="0">
-        <v>0.60835346036413496</v>
+        <v>0.6082602594408848</v>
       </c>
       <c r="S6" s="0">
-        <v>1.1760488381995153</v>
+        <v>0.93201154746934767</v>
       </c>
       <c r="T6" s="0">
-        <v>0.089499999999999858</v>
+        <v>0.079500000000000071</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0089991000899910002</v>
+        <v>0.0079992000799920006</v>
       </c>
       <c r="V6" s="0">
         <v>0.00037478559310910598</v>
       </c>
       <c r="W6" s="0">
-        <v>0.1224799</v>
+        <v>0.035767399999999998</v>
       </c>
       <c r="X6" s="0">
-        <v>12.246765323467653</v>
+        <v>35.731668331668331</v>
       </c>
       <c r="Y6" s="0">
-        <v>0</v>
+        <v>0.1260907</v>
       </c>
       <c r="Z6" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA6" s="0">
+      <c r="AD6" s="0">
         <v>-0.056130873014615418</v>
       </c>
-      <c r="AB6" s="0">
+      <c r="AE6" s="0">
         <v>-0.017397652624266555</v>
       </c>
-      <c r="AC6" s="0">
+      <c r="AF6" s="0">
         <v>0.095327095632060238</v>
       </c>
-      <c r="AD6" s="0">
+      <c r="AG6" s="0">
         <v>2.5333941298887757</v>
       </c>
-      <c r="AE6" s="0">
+      <c r="AH6" s="0">
         <v>0.60946739476013612</v>
       </c>
-      <c r="AF6" s="0">
+      <c r="AI6" s="0">
         <v>8.9377524711883503</v>
       </c>
-      <c r="AG6" s="0">
+      <c r="AJ6" s="0">
         <v>3.3962821780378363</v>
       </c>
-      <c r="AH6" s="0">
+      <c r="AK6" s="0">
         <v>0.28234303636905489</v>
       </c>
-      <c r="AI6" s="0">
+      <c r="AL6" s="0">
         <v>0.058250114865858293</v>
       </c>
-      <c r="AJ6" s="0">
+      <c r="AM6" s="0">
         <v>2026</v>
       </c>
     </row>
@@ -7551,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>20</v>
@@ -7614,45 +8238,54 @@
         <v>10</v>
       </c>
       <c r="W7" s="0">
-        <v>0.097706899999999999</v>
+        <v>0.017337800000000098</v>
       </c>
       <c r="X7" s="0">
-        <v>9.7697130286971294</v>
+        <v>17.320479520479619</v>
       </c>
       <c r="Y7" s="0">
-        <v>1</v>
+        <v>0.1020374</v>
       </c>
       <c r="Z7" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA7" s="0">
+      <c r="AD7" s="0">
         <v>0.06031345168353669</v>
       </c>
-      <c r="AB7" s="0">
+      <c r="AE7" s="0">
         <v>0.080790082225112719</v>
       </c>
-      <c r="AC7" s="0">
+      <c r="AF7" s="0">
         <v>0.056133315758062713</v>
       </c>
-      <c r="AD7" s="0">
+      <c r="AG7" s="0">
         <v>7.2498552885897549</v>
       </c>
-      <c r="AE7" s="0">
+      <c r="AH7" s="0">
         <v>0.65038008840816941</v>
       </c>
-      <c r="AF7" s="0">
+      <c r="AI7" s="0">
         <v>-4.5498225107356998</v>
       </c>
-      <c r="AG7" s="0">
+      <c r="AJ7" s="0">
         <v>4.6835404504001206</v>
       </c>
-      <c r="AH7" s="0">
+      <c r="AK7" s="0">
         <v>0.14627327224925782</v>
       </c>
-      <c r="AI7" s="0">
+      <c r="AL7" s="0">
         <v>0.34605536648269675</v>
       </c>
-      <c r="AJ7" s="0">
+      <c r="AM7" s="0">
         <v>2027</v>
       </c>
     </row>
@@ -7661,7 +8294,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>20</v>
@@ -7722,45 +8355,54 @@
         <v>0.00018627735062182182</v>
       </c>
       <c r="W8" s="0">
-        <v>0.10815760000000001</v>
+        <v>0.020073500000000199</v>
       </c>
       <c r="X8" s="0">
-        <v>10.814678532146786</v>
+        <v>20.053446553446754</v>
       </c>
       <c r="Y8" s="0">
-        <v>1</v>
+        <v>0.10077129999999999</v>
       </c>
       <c r="Z8" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA8" s="0">
+      <c r="AD8" s="0">
         <v>0.06031345168353669</v>
       </c>
-      <c r="AB8" s="0">
+      <c r="AE8" s="0">
         <v>0.080790082225112719</v>
       </c>
-      <c r="AC8" s="0">
+      <c r="AF8" s="0">
         <v>0.056133315758062713</v>
       </c>
-      <c r="AD8" s="0">
+      <c r="AG8" s="0">
         <v>7.2498552885897549</v>
       </c>
-      <c r="AE8" s="0">
+      <c r="AH8" s="0">
         <v>0.65038008840816941</v>
       </c>
-      <c r="AF8" s="0">
+      <c r="AI8" s="0">
         <v>-4.5498225107356998</v>
       </c>
-      <c r="AG8" s="0">
+      <c r="AJ8" s="0">
         <v>4.6835404504001206</v>
       </c>
-      <c r="AH8" s="0">
+      <c r="AK8" s="0">
         <v>0.14627327224925782</v>
       </c>
-      <c r="AI8" s="0">
+      <c r="AL8" s="0">
         <v>0.34605536648269675</v>
       </c>
-      <c r="AJ8" s="0">
+      <c r="AM8" s="0">
         <v>2027</v>
       </c>
     </row>
@@ -7769,7 +8411,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>20</v>
@@ -7830,45 +8472,54 @@
         <v>0.00018627735062182182</v>
       </c>
       <c r="W9" s="0">
-        <v>0.15901370000000001</v>
+        <v>0.066190100000000029</v>
       </c>
       <c r="X9" s="0">
-        <v>15.899780021997799</v>
+        <v>66.123976023976056</v>
       </c>
       <c r="Y9" s="0">
-        <v>1</v>
+        <v>0.1553949</v>
       </c>
       <c r="Z9" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA9" s="0">
+      <c r="AD9" s="0">
         <v>0.06031345168353669</v>
       </c>
-      <c r="AB9" s="0">
+      <c r="AE9" s="0">
         <v>0.080790082225112719</v>
       </c>
-      <c r="AC9" s="0">
+      <c r="AF9" s="0">
         <v>0.056133315758062713</v>
       </c>
-      <c r="AD9" s="0">
+      <c r="AG9" s="0">
         <v>7.2498552885897549</v>
       </c>
-      <c r="AE9" s="0">
+      <c r="AH9" s="0">
         <v>0.65038008840816941</v>
       </c>
-      <c r="AF9" s="0">
+      <c r="AI9" s="0">
         <v>-4.5498225107356998</v>
       </c>
-      <c r="AG9" s="0">
+      <c r="AJ9" s="0">
         <v>4.6835404504001206</v>
       </c>
-      <c r="AH9" s="0">
+      <c r="AK9" s="0">
         <v>0.14627327224925782</v>
       </c>
-      <c r="AI9" s="0">
+      <c r="AL9" s="0">
         <v>0.34605536648269675</v>
       </c>
-      <c r="AJ9" s="0">
+      <c r="AM9" s="0">
         <v>2027</v>
       </c>
     </row>
@@ -7877,7 +8528,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>20</v>
@@ -7896,7 +8547,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="0">
-        <v>0.94529709319015454</v>
+        <v>0.9461556054267376</v>
       </c>
       <c r="J10" s="0">
         <v>7.2498552885897549</v>
@@ -7905,28 +8556,28 @@
         <v>0.12653384507901491</v>
       </c>
       <c r="L10" s="0">
-        <v>0.1910523980909295</v>
+        <v>0.19121947410377857</v>
       </c>
       <c r="M10" s="0">
         <v>1.5050000000000001</v>
       </c>
       <c r="N10" s="0">
-        <v>2.0147192725619636</v>
+        <v>2.011719018584349</v>
       </c>
       <c r="O10" s="0">
-        <v>0.0086172378604829625</v>
+        <v>0.008542611313188897</v>
       </c>
       <c r="P10" s="0">
-        <v>2.7570000000000001</v>
+        <v>2.7560000000000002</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.0083910803301581183</v>
+        <v>0.0083077178128553308</v>
       </c>
       <c r="R10" s="0">
-        <v>0.64176285054768645</v>
+        <v>0.64183747709498051</v>
       </c>
       <c r="S10" s="0">
-        <v>0.40793077909025904</v>
+        <v>0.41109650245711093</v>
       </c>
       <c r="T10" s="0">
         <v>0.049500000000000072</v>
@@ -7938,45 +8589,54 @@
         <v>0.00018627735062182182</v>
       </c>
       <c r="W10" s="0">
-        <v>0.098679799999999998</v>
+        <v>0.013021900000000039</v>
       </c>
       <c r="X10" s="0">
-        <v>9.8669933006699324</v>
+        <v>13.008891108891147</v>
       </c>
       <c r="Y10" s="0">
-        <v>1</v>
+        <v>0.093194799999999994</v>
       </c>
       <c r="Z10" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA10" s="0">
+      <c r="AD10" s="0">
         <v>0.06031345168353669</v>
       </c>
-      <c r="AB10" s="0">
+      <c r="AE10" s="0">
         <v>0.080790082225112719</v>
       </c>
-      <c r="AC10" s="0">
+      <c r="AF10" s="0">
         <v>0.056133315758062713</v>
       </c>
-      <c r="AD10" s="0">
+      <c r="AG10" s="0">
         <v>7.2498552885897549</v>
       </c>
-      <c r="AE10" s="0">
+      <c r="AH10" s="0">
         <v>0.65038008840816941</v>
       </c>
-      <c r="AF10" s="0">
+      <c r="AI10" s="0">
         <v>-4.5498225107356998</v>
       </c>
-      <c r="AG10" s="0">
+      <c r="AJ10" s="0">
         <v>4.6835404504001206</v>
       </c>
-      <c r="AH10" s="0">
+      <c r="AK10" s="0">
         <v>0.14627327224925782</v>
       </c>
-      <c r="AI10" s="0">
+      <c r="AL10" s="0">
         <v>0.34605536648269675</v>
       </c>
-      <c r="AJ10" s="0">
+      <c r="AM10" s="0">
         <v>2027</v>
       </c>
     </row>
@@ -7985,7 +8645,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>20</v>
@@ -8004,7 +8664,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="0">
-        <v>1.2440208088484084</v>
+        <v>1.2405798890804014</v>
       </c>
       <c r="J11" s="0">
         <v>7.2498552885897549</v>
@@ -8013,78 +8673,87 @@
         <v>0.12653384507901491</v>
       </c>
       <c r="L11" s="0">
-        <v>0.26268225857417504</v>
+        <v>0.26282457174155638</v>
       </c>
       <c r="M11" s="0">
-        <v>1.762</v>
+        <v>1.756</v>
       </c>
       <c r="N11" s="0">
-        <v>1.979833580494639</v>
+        <v>1.9733500060249789</v>
       </c>
       <c r="O11" s="0">
-        <v>0.0011552039462414676</v>
+        <v>0.0012293449289431102</v>
       </c>
       <c r="P11" s="0">
-        <v>2.6970000000000001</v>
+        <v>2.694</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.0024630403149317193</v>
+        <v>0.0025215454247990987</v>
       </c>
       <c r="R11" s="0">
-        <v>0.64922488446192794</v>
+        <v>0.6491507434792263</v>
       </c>
       <c r="S11" s="0">
-        <v>0.97650525479623596</v>
+        <v>0.97975727482492447</v>
       </c>
       <c r="T11" s="0">
-        <v>0.069500000000000478</v>
+        <v>0.079500000000000473</v>
       </c>
       <c r="U11" s="0">
-        <v>0.006999300069993001</v>
+        <v>0.0079992000799920006</v>
       </c>
       <c r="V11" s="0">
         <v>0.00018627735062182182</v>
       </c>
       <c r="W11" s="0">
-        <v>0.14397689999999999</v>
+        <v>0.029264599999999977</v>
       </c>
       <c r="X11" s="0">
-        <v>14.396250374962504</v>
+        <v>29.235364635364615</v>
       </c>
       <c r="Y11" s="0">
-        <v>1</v>
+        <v>0.1124671</v>
       </c>
       <c r="Z11" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA11" s="0">
+      <c r="AD11" s="0">
         <v>0.06031345168353669</v>
       </c>
-      <c r="AB11" s="0">
+      <c r="AE11" s="0">
         <v>0.080790082225112719</v>
       </c>
-      <c r="AC11" s="0">
+      <c r="AF11" s="0">
         <v>0.056133315758062713</v>
       </c>
-      <c r="AD11" s="0">
+      <c r="AG11" s="0">
         <v>7.2498552885897549</v>
       </c>
-      <c r="AE11" s="0">
+      <c r="AH11" s="0">
         <v>0.65038008840816941</v>
       </c>
-      <c r="AF11" s="0">
+      <c r="AI11" s="0">
         <v>-4.5498225107356998</v>
       </c>
-      <c r="AG11" s="0">
+      <c r="AJ11" s="0">
         <v>4.6835404504001206</v>
       </c>
-      <c r="AH11" s="0">
+      <c r="AK11" s="0">
         <v>0.14627327224925782</v>
       </c>
-      <c r="AI11" s="0">
+      <c r="AL11" s="0">
         <v>0.34605536648269675</v>
       </c>
-      <c r="AJ11" s="0">
+      <c r="AM11" s="0">
         <v>2027</v>
       </c>
     </row>
@@ -8093,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>20</v>
@@ -8156,45 +8825,54 @@
         <v>10</v>
       </c>
       <c r="W12" s="0">
-        <v>0.099200499999999997</v>
+        <v>0.014553000000000062</v>
       </c>
       <c r="X12" s="0">
-        <v>9.9190580941905804</v>
+        <v>14.538461538461601</v>
       </c>
       <c r="Y12" s="0">
+        <v>0.093538999999999997</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB12" s="0">
         <v>2</v>
       </c>
-      <c r="Z12" s="0">
+      <c r="AC12" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA12" s="0">
+      <c r="AD12" s="0">
         <v>-0.083087562498683265</v>
       </c>
-      <c r="AB12" s="0">
+      <c r="AE12" s="0">
         <v>-0.064982410228961188</v>
       </c>
-      <c r="AC12" s="0">
+      <c r="AF12" s="0">
         <v>0.036315279084250141</v>
       </c>
-      <c r="AD12" s="0">
+      <c r="AG12" s="0">
         <v>3.5767969570477236</v>
       </c>
-      <c r="AE12" s="0">
+      <c r="AH12" s="0">
         <v>0.69801215015698981</v>
       </c>
-      <c r="AF12" s="0">
+      <c r="AI12" s="0">
         <v>5.6735790150049716</v>
       </c>
-      <c r="AG12" s="0">
+      <c r="AJ12" s="0">
         <v>3.9057218301460721</v>
       </c>
-      <c r="AH12" s="0">
+      <c r="AK12" s="0">
         <v>0.2196052781832844</v>
       </c>
-      <c r="AI12" s="0">
+      <c r="AL12" s="0">
         <v>0.33226189323720423</v>
       </c>
-      <c r="AJ12" s="0">
+      <c r="AM12" s="0">
         <v>2028</v>
       </c>
     </row>
@@ -8203,7 +8881,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>20</v>
@@ -8264,45 +8942,54 @@
         <v>0.00067289167064377153</v>
       </c>
       <c r="W13" s="0">
-        <v>0.11481520000000001</v>
+        <v>0.020880200000000154</v>
       </c>
       <c r="X13" s="0">
-        <v>11.480371962803719</v>
+        <v>20.859340659340813</v>
       </c>
       <c r="Y13" s="0">
+        <v>0.1017501</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB13" s="0">
         <v>2</v>
       </c>
-      <c r="Z13" s="0">
+      <c r="AC13" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA13" s="0">
+      <c r="AD13" s="0">
         <v>-0.083087562498683265</v>
       </c>
-      <c r="AB13" s="0">
+      <c r="AE13" s="0">
         <v>-0.064982410228961188</v>
       </c>
-      <c r="AC13" s="0">
+      <c r="AF13" s="0">
         <v>0.036315279084250141</v>
       </c>
-      <c r="AD13" s="0">
+      <c r="AG13" s="0">
         <v>3.5767969570477236</v>
       </c>
-      <c r="AE13" s="0">
+      <c r="AH13" s="0">
         <v>0.69801215015698981</v>
       </c>
-      <c r="AF13" s="0">
+      <c r="AI13" s="0">
         <v>5.6735790150049716</v>
       </c>
-      <c r="AG13" s="0">
+      <c r="AJ13" s="0">
         <v>3.9057218301460721</v>
       </c>
-      <c r="AH13" s="0">
+      <c r="AK13" s="0">
         <v>0.2196052781832844</v>
       </c>
-      <c r="AI13" s="0">
+      <c r="AL13" s="0">
         <v>0.33226189323720423</v>
       </c>
-      <c r="AJ13" s="0">
+      <c r="AM13" s="0">
         <v>2028</v>
       </c>
     </row>
@@ -8311,7 +8998,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>20</v>
@@ -8372,45 +9059,54 @@
         <v>0.00067289167064377153</v>
       </c>
       <c r="W14" s="0">
-        <v>0.16841400000000001</v>
+        <v>0.061606700000000007</v>
       </c>
       <c r="X14" s="0">
-        <v>16.839716028397159</v>
+        <v>61.545154845154855</v>
       </c>
       <c r="Y14" s="0">
+        <v>0.14820710000000001</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB14" s="0">
         <v>2</v>
       </c>
-      <c r="Z14" s="0">
+      <c r="AC14" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA14" s="0">
+      <c r="AD14" s="0">
         <v>-0.083087562498683265</v>
       </c>
-      <c r="AB14" s="0">
+      <c r="AE14" s="0">
         <v>-0.064982410228961188</v>
       </c>
-      <c r="AC14" s="0">
+      <c r="AF14" s="0">
         <v>0.036315279084250141</v>
       </c>
-      <c r="AD14" s="0">
+      <c r="AG14" s="0">
         <v>3.5767969570477236</v>
       </c>
-      <c r="AE14" s="0">
+      <c r="AH14" s="0">
         <v>0.69801215015698981</v>
       </c>
-      <c r="AF14" s="0">
+      <c r="AI14" s="0">
         <v>5.6735790150049716</v>
       </c>
-      <c r="AG14" s="0">
+      <c r="AJ14" s="0">
         <v>3.9057218301460721</v>
       </c>
-      <c r="AH14" s="0">
+      <c r="AK14" s="0">
         <v>0.2196052781832844</v>
       </c>
-      <c r="AI14" s="0">
+      <c r="AL14" s="0">
         <v>0.33226189323720423</v>
       </c>
-      <c r="AJ14" s="0">
+      <c r="AM14" s="0">
         <v>2028</v>
       </c>
     </row>
@@ -8419,7 +9115,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>20</v>
@@ -8438,37 +9134,37 @@
         <v>10</v>
       </c>
       <c r="I15" s="0">
-        <v>0.90172204611954243</v>
+        <v>0.90402384037053407</v>
       </c>
       <c r="J15" s="0">
-        <v>4.2633879013585867</v>
+        <v>4.3059943516153192</v>
       </c>
       <c r="K15" s="0">
-        <v>0.074410156168398564</v>
+        <v>0.075153779007965729</v>
       </c>
       <c r="L15" s="0">
-        <v>0.19071618948876457</v>
+        <v>0.19073828111367225</v>
       </c>
       <c r="M15" s="0">
-        <v>1.5290000000000001</v>
+        <v>1.5270000000000001</v>
       </c>
       <c r="N15" s="0">
-        <v>2.2594417816040786</v>
+        <v>2.2886289135032172</v>
       </c>
       <c r="O15" s="0">
-        <v>0.0066930271213685444</v>
+        <v>0.0071609948383770661</v>
       </c>
       <c r="P15" s="0">
-        <v>2.8210000000000002</v>
+        <v>2.8250000000000002</v>
       </c>
       <c r="Q15" s="0">
         <v>0</v>
       </c>
       <c r="R15" s="0">
-        <v>0.69131912303562126</v>
+        <v>0.69085115531861274</v>
       </c>
       <c r="S15" s="0">
-        <v>0.48871505549744143</v>
+        <v>0.40762683344151485</v>
       </c>
       <c r="T15" s="0">
         <v>0.039500000000000077</v>
@@ -8480,45 +9176,54 @@
         <v>0.00067289167064377153</v>
       </c>
       <c r="W15" s="0">
-        <v>0.092658500000000005</v>
+        <v>0.012519100000000028</v>
       </c>
       <c r="X15" s="0">
-        <v>9.264923507649236</v>
+        <v>12.506593406593433</v>
       </c>
       <c r="Y15" s="0">
+        <v>0.091935299999999998</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB15" s="0">
         <v>2</v>
       </c>
-      <c r="Z15" s="0">
+      <c r="AC15" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA15" s="0">
+      <c r="AD15" s="0">
         <v>-0.083087562498683265</v>
       </c>
-      <c r="AB15" s="0">
+      <c r="AE15" s="0">
         <v>-0.064982410228961188</v>
       </c>
-      <c r="AC15" s="0">
+      <c r="AF15" s="0">
         <v>0.036315279084250141</v>
       </c>
-      <c r="AD15" s="0">
+      <c r="AG15" s="0">
         <v>3.5767969570477236</v>
       </c>
-      <c r="AE15" s="0">
+      <c r="AH15" s="0">
         <v>0.69801215015698981</v>
       </c>
-      <c r="AF15" s="0">
+      <c r="AI15" s="0">
         <v>5.6735790150049716</v>
       </c>
-      <c r="AG15" s="0">
+      <c r="AJ15" s="0">
         <v>3.9057218301460721</v>
       </c>
-      <c r="AH15" s="0">
+      <c r="AK15" s="0">
         <v>0.2196052781832844</v>
       </c>
-      <c r="AI15" s="0">
+      <c r="AL15" s="0">
         <v>0.33226189323720423</v>
       </c>
-      <c r="AJ15" s="0">
+      <c r="AM15" s="0">
         <v>2028</v>
       </c>
     </row>
@@ -8527,7 +9232,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>20</v>
@@ -8546,87 +9251,96 @@
         <v>10</v>
       </c>
       <c r="I16" s="0">
-        <v>1.0807045598120588</v>
+        <v>1.0785667862142316</v>
       </c>
       <c r="J16" s="0">
-        <v>4.2345123005820824</v>
+        <v>4.2479625852966212</v>
       </c>
       <c r="K16" s="0">
-        <v>0.073906181861357126</v>
+        <v>0.074140933614956495</v>
       </c>
       <c r="L16" s="0">
-        <v>0.26598401530467908</v>
+        <v>0.26936282742530937</v>
       </c>
       <c r="M16" s="0">
-        <v>1.764</v>
+        <v>1.7530000000000001</v>
       </c>
       <c r="N16" s="0">
-        <v>2.0955741921067155</v>
+        <v>2.0828591285303135</v>
       </c>
       <c r="O16" s="0">
-        <v>0.0017906170849335545</v>
+        <v>0.0016646506767692415</v>
       </c>
       <c r="P16" s="0">
-        <v>2.762</v>
+        <v>2.7549999999999999</v>
       </c>
       <c r="Q16" s="0">
-        <v>0.0039185022490757504</v>
+        <v>0.0038973424800349266</v>
       </c>
       <c r="R16" s="0">
-        <v>0.69980276724192336</v>
+        <v>0.69967680083375905</v>
       </c>
       <c r="S16" s="0">
-        <v>1.0706151735565597</v>
+        <v>0.84723702581678806</v>
       </c>
       <c r="T16" s="0">
-        <v>0.029500000000000009</v>
+        <v>0.039500000000000243</v>
       </c>
       <c r="U16" s="0">
-        <v>0.0029997000299970002</v>
+        <v>0.0039996000399960003</v>
       </c>
       <c r="V16" s="0">
         <v>0.00067289167064377153</v>
       </c>
       <c r="W16" s="0">
-        <v>0.1147635</v>
+        <v>0.034980100000000021</v>
       </c>
       <c r="X16" s="0">
-        <v>11.475202479752024</v>
+        <v>34.945154845154867</v>
       </c>
       <c r="Y16" s="0">
+        <v>0.1242447</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB16" s="0">
         <v>2</v>
       </c>
-      <c r="Z16" s="0">
+      <c r="AC16" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA16" s="0">
+      <c r="AD16" s="0">
         <v>-0.083087562498683265</v>
       </c>
-      <c r="AB16" s="0">
+      <c r="AE16" s="0">
         <v>-0.064982410228961188</v>
       </c>
-      <c r="AC16" s="0">
+      <c r="AF16" s="0">
         <v>0.036315279084250141</v>
       </c>
-      <c r="AD16" s="0">
+      <c r="AG16" s="0">
         <v>3.5767969570477236</v>
       </c>
-      <c r="AE16" s="0">
+      <c r="AH16" s="0">
         <v>0.69801215015698981</v>
       </c>
-      <c r="AF16" s="0">
+      <c r="AI16" s="0">
         <v>5.6735790150049716</v>
       </c>
-      <c r="AG16" s="0">
+      <c r="AJ16" s="0">
         <v>3.9057218301460721</v>
       </c>
-      <c r="AH16" s="0">
+      <c r="AK16" s="0">
         <v>0.2196052781832844</v>
       </c>
-      <c r="AI16" s="0">
+      <c r="AL16" s="0">
         <v>0.33226189323720423</v>
       </c>
-      <c r="AJ16" s="0">
+      <c r="AM16" s="0">
         <v>2028</v>
       </c>
     </row>
@@ -8635,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>20</v>
@@ -8698,45 +9412,54 @@
         <v>10</v>
       </c>
       <c r="W17" s="0">
-        <v>0.095890600000000006</v>
+        <v>0.014953300000000043</v>
       </c>
       <c r="X17" s="0">
-        <v>9.5881011898810122</v>
+        <v>14.93836163836168</v>
       </c>
       <c r="Y17" s="0">
+        <v>0.093888100000000002</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB17" s="0">
         <v>3</v>
       </c>
-      <c r="Z17" s="0">
+      <c r="AC17" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA17" s="0">
+      <c r="AD17" s="0">
         <v>-0.072447765317326537</v>
       </c>
-      <c r="AB17" s="0">
+      <c r="AE17" s="0">
         <v>-0.047198813521273357</v>
       </c>
-      <c r="AC17" s="0">
+      <c r="AF17" s="0">
         <v>0.077089539387445422</v>
       </c>
-      <c r="AD17" s="0">
+      <c r="AG17" s="0">
         <v>5.7412264416893075</v>
       </c>
-      <c r="AE17" s="0">
+      <c r="AH17" s="0">
         <v>0.58754708914947662</v>
       </c>
-      <c r="AF17" s="0">
+      <c r="AI17" s="0">
         <v>-6.7591489980797555</v>
       </c>
-      <c r="AG17" s="0">
+      <c r="AJ17" s="0">
         <v>4.7051828449319979</v>
       </c>
-      <c r="AH17" s="0">
+      <c r="AK17" s="0">
         <v>0.19004622616115316</v>
       </c>
-      <c r="AI17" s="0">
+      <c r="AL17" s="0">
         <v>0.21484249439727565</v>
       </c>
-      <c r="AJ17" s="0">
+      <c r="AM17" s="0">
         <v>2029</v>
       </c>
     </row>
@@ -8745,7 +9468,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>20</v>
@@ -8806,45 +9529,54 @@
         <v>0.00077092890684848925</v>
       </c>
       <c r="W18" s="0">
-        <v>0.1012216</v>
+        <v>0.02063420000000003</v>
       </c>
       <c r="X18" s="0">
-        <v>10.12114788521148</v>
+        <v>20.613586413586443</v>
       </c>
       <c r="Y18" s="0">
+        <v>0.1027638</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB18" s="0">
         <v>3</v>
       </c>
-      <c r="Z18" s="0">
+      <c r="AC18" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA18" s="0">
+      <c r="AD18" s="0">
         <v>-0.072447765317326537</v>
       </c>
-      <c r="AB18" s="0">
+      <c r="AE18" s="0">
         <v>-0.047198813521273357</v>
       </c>
-      <c r="AC18" s="0">
+      <c r="AF18" s="0">
         <v>0.077089539387445422</v>
       </c>
-      <c r="AD18" s="0">
+      <c r="AG18" s="0">
         <v>5.7412264416893075</v>
       </c>
-      <c r="AE18" s="0">
+      <c r="AH18" s="0">
         <v>0.58754708914947662</v>
       </c>
-      <c r="AF18" s="0">
+      <c r="AI18" s="0">
         <v>-6.7591489980797555</v>
       </c>
-      <c r="AG18" s="0">
+      <c r="AJ18" s="0">
         <v>4.7051828449319979</v>
       </c>
-      <c r="AH18" s="0">
+      <c r="AK18" s="0">
         <v>0.19004622616115316</v>
       </c>
-      <c r="AI18" s="0">
+      <c r="AL18" s="0">
         <v>0.21484249439727565</v>
       </c>
-      <c r="AJ18" s="0">
+      <c r="AM18" s="0">
         <v>2029</v>
       </c>
     </row>
@@ -8853,7 +9585,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>20</v>
@@ -8914,45 +9646,54 @@
         <v>0.00077092890684848925</v>
       </c>
       <c r="W19" s="0">
-        <v>0.1487887</v>
+        <v>0.060702699999999985</v>
       </c>
       <c r="X19" s="0">
-        <v>14.877382261773823</v>
+        <v>60.642057942057924</v>
       </c>
       <c r="Y19" s="0">
+        <v>0.1466383</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB19" s="0">
         <v>3</v>
       </c>
-      <c r="Z19" s="0">
+      <c r="AC19" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA19" s="0">
+      <c r="AD19" s="0">
         <v>-0.072447765317326537</v>
       </c>
-      <c r="AB19" s="0">
+      <c r="AE19" s="0">
         <v>-0.047198813521273357</v>
       </c>
-      <c r="AC19" s="0">
+      <c r="AF19" s="0">
         <v>0.077089539387445422</v>
       </c>
-      <c r="AD19" s="0">
+      <c r="AG19" s="0">
         <v>5.7412264416893075</v>
       </c>
-      <c r="AE19" s="0">
+      <c r="AH19" s="0">
         <v>0.58754708914947662</v>
       </c>
-      <c r="AF19" s="0">
+      <c r="AI19" s="0">
         <v>-6.7591489980797555</v>
       </c>
-      <c r="AG19" s="0">
+      <c r="AJ19" s="0">
         <v>4.7051828449319979</v>
       </c>
-      <c r="AH19" s="0">
+      <c r="AK19" s="0">
         <v>0.19004622616115316</v>
       </c>
-      <c r="AI19" s="0">
+      <c r="AL19" s="0">
         <v>0.21484249439727565</v>
       </c>
-      <c r="AJ19" s="0">
+      <c r="AM19" s="0">
         <v>2029</v>
       </c>
     </row>
@@ -8961,7 +9702,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>20</v>
@@ -8980,7 +9721,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="0">
-        <v>0.81717964977435143</v>
+        <v>0.81930736400975257</v>
       </c>
       <c r="J20" s="0">
         <v>5.7412264416893075</v>
@@ -8989,28 +9730,28 @@
         <v>0.10020330451003666</v>
       </c>
       <c r="L20" s="0">
-        <v>0.17890263405040036</v>
+        <v>0.18262351284466577</v>
       </c>
       <c r="M20" s="0">
-        <v>1.4650000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="N20" s="0">
-        <v>1.8298249191595848</v>
+        <v>1.8482583820552021</v>
       </c>
       <c r="O20" s="0">
-        <v>0.0052022517140765112</v>
+        <v>0.0055713134818898835</v>
       </c>
       <c r="P20" s="0">
-        <v>2.6779999999999999</v>
+        <v>2.681</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.014680267082578635</v>
+        <v>0.01560774881628868</v>
       </c>
       <c r="R20" s="0">
-        <v>0.58234483743540011</v>
+        <v>0.58197577566758674</v>
       </c>
       <c r="S20" s="0">
-        <v>0.4722449454772662</v>
+        <v>0.38352994505501314</v>
       </c>
       <c r="T20" s="0">
         <v>0.049500000000000072</v>
@@ -9022,45 +9763,54 @@
         <v>0.00077092890684848925</v>
       </c>
       <c r="W20" s="0">
-        <v>0.094067499999999998</v>
+        <v>0.012065300000000003</v>
       </c>
       <c r="X20" s="0">
-        <v>9.4058094190580945</v>
+        <v>12.053246753246757</v>
       </c>
       <c r="Y20" s="0">
+        <v>0.091445100000000001</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB20" s="0">
         <v>3</v>
       </c>
-      <c r="Z20" s="0">
+      <c r="AC20" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA20" s="0">
+      <c r="AD20" s="0">
         <v>-0.072447765317326537</v>
       </c>
-      <c r="AB20" s="0">
+      <c r="AE20" s="0">
         <v>-0.047198813521273357</v>
       </c>
-      <c r="AC20" s="0">
+      <c r="AF20" s="0">
         <v>0.077089539387445422</v>
       </c>
-      <c r="AD20" s="0">
+      <c r="AG20" s="0">
         <v>5.7412264416893075</v>
       </c>
-      <c r="AE20" s="0">
+      <c r="AH20" s="0">
         <v>0.58754708914947662</v>
       </c>
-      <c r="AF20" s="0">
+      <c r="AI20" s="0">
         <v>-6.7591489980797555</v>
       </c>
-      <c r="AG20" s="0">
+      <c r="AJ20" s="0">
         <v>4.7051828449319979</v>
       </c>
-      <c r="AH20" s="0">
+      <c r="AK20" s="0">
         <v>0.19004622616115316</v>
       </c>
-      <c r="AI20" s="0">
+      <c r="AL20" s="0">
         <v>0.21484249439727565</v>
       </c>
-      <c r="AJ20" s="0">
+      <c r="AM20" s="0">
         <v>2029</v>
       </c>
     </row>
@@ -9069,7 +9819,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>20</v>
@@ -9088,7 +9838,7 @@
         <v>10</v>
       </c>
       <c r="I21" s="0">
-        <v>1.0650777423364191</v>
+        <v>1.0583838238887415</v>
       </c>
       <c r="J21" s="0">
         <v>5.7412264416893075</v>
@@ -9097,78 +9847,87 @@
         <v>0.10020330451003666</v>
       </c>
       <c r="L21" s="0">
-        <v>0.24508694485735563</v>
+        <v>0.25183967825697085</v>
       </c>
       <c r="M21" s="0">
-        <v>1.724</v>
+        <v>1.7070000000000001</v>
       </c>
       <c r="N21" s="0">
-        <v>1.7961459381388414</v>
+        <v>1.7818788505836611</v>
       </c>
       <c r="O21" s="0">
-        <v>0.00021625579956252583</v>
+        <v>0.00026349970318739757</v>
       </c>
       <c r="P21" s="0">
-        <v>2.6320000000000001</v>
+        <v>2.6190000000000002</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.0057170705133742228</v>
+        <v>0.0062710389557545376</v>
       </c>
       <c r="R21" s="0">
-        <v>0.58776334494903915</v>
+        <v>0.58781058885266402</v>
       </c>
       <c r="S21" s="0">
-        <v>1.0601207170746374</v>
+        <v>0.82339773409762151</v>
       </c>
       <c r="T21" s="0">
-        <v>0.079500000000000487</v>
+        <v>0.069500000000000256</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0079992000799920006</v>
+        <v>0.006999300069993001</v>
       </c>
       <c r="V21" s="0">
         <v>0.00077092890684848925</v>
       </c>
       <c r="W21" s="0">
-        <v>0.112049</v>
+        <v>0.028850300000000044</v>
       </c>
       <c r="X21" s="0">
-        <v>11.203779622037796</v>
+        <v>28.821478521478568</v>
       </c>
       <c r="Y21" s="0">
+        <v>0.1115165</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB21" s="0">
         <v>3</v>
       </c>
-      <c r="Z21" s="0">
+      <c r="AC21" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA21" s="0">
+      <c r="AD21" s="0">
         <v>-0.072447765317326537</v>
       </c>
-      <c r="AB21" s="0">
+      <c r="AE21" s="0">
         <v>-0.047198813521273357</v>
       </c>
-      <c r="AC21" s="0">
+      <c r="AF21" s="0">
         <v>0.077089539387445422</v>
       </c>
-      <c r="AD21" s="0">
+      <c r="AG21" s="0">
         <v>5.7412264416893075</v>
       </c>
-      <c r="AE21" s="0">
+      <c r="AH21" s="0">
         <v>0.58754708914947662</v>
       </c>
-      <c r="AF21" s="0">
+      <c r="AI21" s="0">
         <v>-6.7591489980797555</v>
       </c>
-      <c r="AG21" s="0">
+      <c r="AJ21" s="0">
         <v>4.7051828449319979</v>
       </c>
-      <c r="AH21" s="0">
+      <c r="AK21" s="0">
         <v>0.19004622616115316</v>
       </c>
-      <c r="AI21" s="0">
+      <c r="AL21" s="0">
         <v>0.21484249439727565</v>
       </c>
-      <c r="AJ21" s="0">
+      <c r="AM21" s="0">
         <v>2029</v>
       </c>
     </row>
@@ -9177,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>20</v>
@@ -9240,45 +9999,54 @@
         <v>10</v>
       </c>
       <c r="W22" s="0">
-        <v>0.0939411</v>
+        <v>0.014582400000000013</v>
       </c>
       <c r="X22" s="0">
-        <v>9.3931706829317054</v>
+        <v>14.567832167832181</v>
       </c>
       <c r="Y22" s="0">
+        <v>0.093649700000000002</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB22" s="0">
         <v>4</v>
       </c>
-      <c r="Z22" s="0">
+      <c r="AC22" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA22" s="0">
+      <c r="AD22" s="0">
         <v>-0.027853941328179907</v>
       </c>
-      <c r="AB22" s="0">
+      <c r="AE22" s="0">
         <v>0.034798095733532902</v>
       </c>
-      <c r="AC22" s="0">
+      <c r="AF22" s="0">
         <v>0.086125608141834953</v>
       </c>
-      <c r="AD22" s="0">
+      <c r="AG22" s="0">
         <v>6.2596364657045527</v>
       </c>
-      <c r="AE22" s="0">
+      <c r="AH22" s="0">
         <v>0.99732601210058935</v>
       </c>
-      <c r="AF22" s="0">
+      <c r="AI22" s="0">
         <v>5.1794446303511013</v>
       </c>
-      <c r="AG22" s="0">
+      <c r="AJ22" s="0">
         <v>4.7792400911684485</v>
       </c>
-      <c r="AH22" s="0">
+      <c r="AK22" s="0">
         <v>0.24189324001209297</v>
       </c>
-      <c r="AI22" s="0">
+      <c r="AL22" s="0">
         <v>0.20258822647070229</v>
       </c>
-      <c r="AJ22" s="0">
+      <c r="AM22" s="0">
         <v>2030</v>
       </c>
     </row>
@@ -9287,7 +10055,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>20</v>
@@ -9348,45 +10116,54 @@
         <v>0.00086666881945873797</v>
       </c>
       <c r="W23" s="0">
-        <v>0.1015533</v>
+        <v>0.020594100000000167</v>
       </c>
       <c r="X23" s="0">
-        <v>10.154314568543146</v>
+        <v>20.573526473526641</v>
       </c>
       <c r="Y23" s="0">
+        <v>0.1019079</v>
+      </c>
+      <c r="Z23" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB23" s="0">
         <v>4</v>
       </c>
-      <c r="Z23" s="0">
+      <c r="AC23" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA23" s="0">
+      <c r="AD23" s="0">
         <v>-0.027853941328179907</v>
       </c>
-      <c r="AB23" s="0">
+      <c r="AE23" s="0">
         <v>0.034798095733532902</v>
       </c>
-      <c r="AC23" s="0">
+      <c r="AF23" s="0">
         <v>0.086125608141834953</v>
       </c>
-      <c r="AD23" s="0">
+      <c r="AG23" s="0">
         <v>6.2596364657045527</v>
       </c>
-      <c r="AE23" s="0">
+      <c r="AH23" s="0">
         <v>0.99732601210058935</v>
       </c>
-      <c r="AF23" s="0">
+      <c r="AI23" s="0">
         <v>5.1794446303511013</v>
       </c>
-      <c r="AG23" s="0">
+      <c r="AJ23" s="0">
         <v>4.7792400911684485</v>
       </c>
-      <c r="AH23" s="0">
+      <c r="AK23" s="0">
         <v>0.24189324001209297</v>
       </c>
-      <c r="AI23" s="0">
+      <c r="AL23" s="0">
         <v>0.20258822647070229</v>
       </c>
-      <c r="AJ23" s="0">
+      <c r="AM23" s="0">
         <v>2030</v>
       </c>
     </row>
@@ -9395,7 +10172,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>20</v>
@@ -9456,45 +10233,54 @@
         <v>0.00086666881945873797</v>
       </c>
       <c r="W24" s="0">
-        <v>0.14941009999999999</v>
+        <v>0.063102600000000078</v>
       </c>
       <c r="X24" s="0">
-        <v>14.939516048395159</v>
+        <v>63.039560439560511</v>
       </c>
       <c r="Y24" s="0">
+        <v>0.15136849999999999</v>
+      </c>
+      <c r="Z24" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB24" s="0">
         <v>4</v>
       </c>
-      <c r="Z24" s="0">
+      <c r="AC24" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA24" s="0">
+      <c r="AD24" s="0">
         <v>-0.027853941328179907</v>
       </c>
-      <c r="AB24" s="0">
+      <c r="AE24" s="0">
         <v>0.034798095733532902</v>
       </c>
-      <c r="AC24" s="0">
+      <c r="AF24" s="0">
         <v>0.086125608141834953</v>
       </c>
-      <c r="AD24" s="0">
+      <c r="AG24" s="0">
         <v>6.2596364657045527</v>
       </c>
-      <c r="AE24" s="0">
+      <c r="AH24" s="0">
         <v>0.99732601210058935</v>
       </c>
-      <c r="AF24" s="0">
+      <c r="AI24" s="0">
         <v>5.1794446303511013</v>
       </c>
-      <c r="AG24" s="0">
+      <c r="AJ24" s="0">
         <v>4.7792400911684485</v>
       </c>
-      <c r="AH24" s="0">
+      <c r="AK24" s="0">
         <v>0.24189324001209297</v>
       </c>
-      <c r="AI24" s="0">
+      <c r="AL24" s="0">
         <v>0.20258822647070229</v>
       </c>
-      <c r="AJ24" s="0">
+      <c r="AM24" s="0">
         <v>2030</v>
       </c>
     </row>
@@ -9503,7 +10289,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>20</v>
@@ -9522,7 +10308,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="0">
-        <v>1.300325750480158</v>
+        <v>1.3031430073309489</v>
       </c>
       <c r="J25" s="0">
         <v>6.2596364657045527</v>
@@ -9531,28 +10317,28 @@
         <v>0.10925126630444555</v>
       </c>
       <c r="L25" s="0">
-        <v>0.27253910009431287</v>
+        <v>0.2739004115493977</v>
       </c>
       <c r="M25" s="0">
-        <v>1.629</v>
+        <v>1.625</v>
       </c>
       <c r="N25" s="0">
-        <v>2.9622074854297424</v>
+        <v>2.9724059681392827</v>
       </c>
       <c r="O25" s="0">
-        <v>0.0053155414819230362</v>
+        <v>0.0054524606514256835</v>
       </c>
       <c r="P25" s="0">
         <v>2.9610000000000003</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.0053582512749412725</v>
+        <v>0.005481244701988075</v>
       </c>
       <c r="R25" s="0">
-        <v>0.99201047061866632</v>
+        <v>0.99187355144916367</v>
       </c>
       <c r="S25" s="0">
-        <v>0.438447487876932</v>
+        <v>0.39650837118925741</v>
       </c>
       <c r="T25" s="0">
         <v>0.05949999999999997</v>
@@ -9564,45 +10350,54 @@
         <v>0.00086666881945873797</v>
       </c>
       <c r="W25" s="0">
-        <v>0.0943803</v>
+        <v>0.013551700000000043</v>
       </c>
       <c r="X25" s="0">
-        <v>9.4370862913708642</v>
+        <v>13.538161838161882</v>
       </c>
       <c r="Y25" s="0">
+        <v>0.095159900000000006</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB25" s="0">
         <v>4</v>
       </c>
-      <c r="Z25" s="0">
+      <c r="AC25" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA25" s="0">
+      <c r="AD25" s="0">
         <v>-0.027853941328179907</v>
       </c>
-      <c r="AB25" s="0">
+      <c r="AE25" s="0">
         <v>0.034798095733532902</v>
       </c>
-      <c r="AC25" s="0">
+      <c r="AF25" s="0">
         <v>0.086125608141834953</v>
       </c>
-      <c r="AD25" s="0">
+      <c r="AG25" s="0">
         <v>6.2596364657045527</v>
       </c>
-      <c r="AE25" s="0">
+      <c r="AH25" s="0">
         <v>0.99732601210058935</v>
       </c>
-      <c r="AF25" s="0">
+      <c r="AI25" s="0">
         <v>5.1794446303511013</v>
       </c>
-      <c r="AG25" s="0">
+      <c r="AJ25" s="0">
         <v>4.7792400911684485</v>
       </c>
-      <c r="AH25" s="0">
+      <c r="AK25" s="0">
         <v>0.24189324001209297</v>
       </c>
-      <c r="AI25" s="0">
+      <c r="AL25" s="0">
         <v>0.20258822647070229</v>
       </c>
-      <c r="AJ25" s="0">
+      <c r="AM25" s="0">
         <v>2030</v>
       </c>
     </row>
@@ -9611,7 +10406,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>20</v>
@@ -9630,7 +10425,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="0">
-        <v>1.6135746476539228</v>
+        <v>1.6051285028678672</v>
       </c>
       <c r="J26" s="0">
         <v>6.2596364657045527</v>
@@ -9639,78 +10434,87 @@
         <v>0.10925126630444555</v>
       </c>
       <c r="L26" s="0">
-        <v>0.360633586441092</v>
+        <v>0.36197936399625813</v>
       </c>
       <c r="M26" s="0">
         <v>3.1190000000000002</v>
       </c>
       <c r="N26" s="0">
-        <v>3.0294052861124752</v>
+        <v>3.0034493121868104</v>
       </c>
       <c r="O26" s="0">
-        <v>0.00071060873868866725</v>
+        <v>0.0008074159574341655</v>
       </c>
       <c r="P26" s="0">
-        <v>2.9570000000000003</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="Q26" s="0">
-        <v>0.0042670875575689937</v>
+        <v>0.0042384582984891228</v>
       </c>
       <c r="R26" s="0">
-        <v>0.99803662083927802</v>
+        <v>0.99813342805802352</v>
       </c>
       <c r="S26" s="0">
-        <v>0.93508725426113393</v>
+        <v>0.80196122579294282</v>
       </c>
       <c r="T26" s="0">
-        <v>0.0695000000000007</v>
+        <v>0.049500000000000231</v>
       </c>
       <c r="U26" s="0">
-        <v>0.006999300069993001</v>
+        <v>0.0049995000499950008</v>
       </c>
       <c r="V26" s="0">
         <v>0.00086666881945873797</v>
       </c>
       <c r="W26" s="0">
-        <v>0.10899150000000001</v>
+        <v>0.029412999999999963</v>
       </c>
       <c r="X26" s="0">
-        <v>10.898060193980603</v>
+        <v>29.383616383616349</v>
       </c>
       <c r="Y26" s="0">
+        <v>0.11356289999999999</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB26" s="0">
         <v>4</v>
       </c>
-      <c r="Z26" s="0">
+      <c r="AC26" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA26" s="0">
+      <c r="AD26" s="0">
         <v>-0.027853941328179907</v>
       </c>
-      <c r="AB26" s="0">
+      <c r="AE26" s="0">
         <v>0.034798095733532902</v>
       </c>
-      <c r="AC26" s="0">
+      <c r="AF26" s="0">
         <v>0.086125608141834953</v>
       </c>
-      <c r="AD26" s="0">
+      <c r="AG26" s="0">
         <v>6.2596364657045527</v>
       </c>
-      <c r="AE26" s="0">
+      <c r="AH26" s="0">
         <v>0.99732601210058935</v>
       </c>
-      <c r="AF26" s="0">
+      <c r="AI26" s="0">
         <v>5.1794446303511013</v>
       </c>
-      <c r="AG26" s="0">
+      <c r="AJ26" s="0">
         <v>4.7792400911684485</v>
       </c>
-      <c r="AH26" s="0">
+      <c r="AK26" s="0">
         <v>0.24189324001209297</v>
       </c>
-      <c r="AI26" s="0">
+      <c r="AL26" s="0">
         <v>0.20258822647070229</v>
       </c>
-      <c r="AJ26" s="0">
+      <c r="AM26" s="0">
         <v>2030</v>
       </c>
     </row>
@@ -9719,7 +10523,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>20</v>
@@ -9782,45 +10586,54 @@
         <v>10</v>
       </c>
       <c r="W27" s="0">
-        <v>0.094459500000000002</v>
+        <v>0.014679200000000031</v>
       </c>
       <c r="X27" s="0">
-        <v>9.4450054994500565</v>
+        <v>14.664535464535495</v>
       </c>
       <c r="Y27" s="0">
+        <v>0.094952300000000003</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB27" s="0">
         <v>5</v>
       </c>
-      <c r="Z27" s="0">
+      <c r="AC27" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA27" s="0">
+      <c r="AD27" s="0">
         <v>-0.024215858070456051</v>
       </c>
-      <c r="AB27" s="0">
+      <c r="AE27" s="0">
         <v>0.035686249116920227</v>
       </c>
-      <c r="AC27" s="0">
+      <c r="AF27" s="0">
         <v>-0.058777780448417444</v>
       </c>
-      <c r="AD27" s="0">
+      <c r="AG27" s="0">
         <v>5.53042749383631</v>
       </c>
-      <c r="AE27" s="0">
+      <c r="AH27" s="0">
         <v>0.82369857747910347</v>
       </c>
-      <c r="AF27" s="0">
+      <c r="AI27" s="0">
         <v>-5.115526398965244</v>
       </c>
-      <c r="AG27" s="0">
+      <c r="AJ27" s="0">
         <v>4.6670959252205817</v>
       </c>
-      <c r="AH27" s="0">
+      <c r="AK27" s="0">
         <v>0.29613695774238835</v>
       </c>
-      <c r="AI27" s="0">
+      <c r="AL27" s="0">
         <v>-0.044607001535815649</v>
       </c>
-      <c r="AJ27" s="0">
+      <c r="AM27" s="0">
         <v>2031</v>
       </c>
     </row>
@@ -9829,7 +10642,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>20</v>
@@ -9890,45 +10703,54 @@
         <v>0.00076711703703047363</v>
       </c>
       <c r="W28" s="0">
-        <v>0.10169930000000001</v>
+        <v>0.021338200000000127</v>
       </c>
       <c r="X28" s="0">
-        <v>10.168913108689132</v>
+        <v>21.316883116883243</v>
       </c>
       <c r="Y28" s="0">
+        <v>0.10303900000000001</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB28" s="0">
         <v>5</v>
       </c>
-      <c r="Z28" s="0">
+      <c r="AC28" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA28" s="0">
+      <c r="AD28" s="0">
         <v>-0.024215858070456051</v>
       </c>
-      <c r="AB28" s="0">
+      <c r="AE28" s="0">
         <v>0.035686249116920227</v>
       </c>
-      <c r="AC28" s="0">
+      <c r="AF28" s="0">
         <v>-0.058777780448417444</v>
       </c>
-      <c r="AD28" s="0">
+      <c r="AG28" s="0">
         <v>5.53042749383631</v>
       </c>
-      <c r="AE28" s="0">
+      <c r="AH28" s="0">
         <v>0.82369857747910347</v>
       </c>
-      <c r="AF28" s="0">
+      <c r="AI28" s="0">
         <v>-5.115526398965244</v>
       </c>
-      <c r="AG28" s="0">
+      <c r="AJ28" s="0">
         <v>4.6670959252205817</v>
       </c>
-      <c r="AH28" s="0">
+      <c r="AK28" s="0">
         <v>0.29613695774238835</v>
       </c>
-      <c r="AI28" s="0">
+      <c r="AL28" s="0">
         <v>-0.044607001535815649</v>
       </c>
-      <c r="AJ28" s="0">
+      <c r="AM28" s="0">
         <v>2031</v>
       </c>
     </row>
@@ -9937,7 +10759,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>20</v>
@@ -9998,45 +10820,54 @@
         <v>0.00076711703703047363</v>
       </c>
       <c r="W29" s="0">
-        <v>0.1475678</v>
+        <v>0.059299399999999877</v>
       </c>
       <c r="X29" s="0">
-        <v>14.755304469553044</v>
+        <v>59.24015984015972</v>
       </c>
       <c r="Y29" s="0">
+        <v>0.1446723</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB29" s="0">
         <v>5</v>
       </c>
-      <c r="Z29" s="0">
+      <c r="AC29" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA29" s="0">
+      <c r="AD29" s="0">
         <v>-0.024215858070456051</v>
       </c>
-      <c r="AB29" s="0">
+      <c r="AE29" s="0">
         <v>0.035686249116920227</v>
       </c>
-      <c r="AC29" s="0">
+      <c r="AF29" s="0">
         <v>-0.058777780448417444</v>
       </c>
-      <c r="AD29" s="0">
+      <c r="AG29" s="0">
         <v>5.53042749383631</v>
       </c>
-      <c r="AE29" s="0">
+      <c r="AH29" s="0">
         <v>0.82369857747910347</v>
       </c>
-      <c r="AF29" s="0">
+      <c r="AI29" s="0">
         <v>-5.115526398965244</v>
       </c>
-      <c r="AG29" s="0">
+      <c r="AJ29" s="0">
         <v>4.6670959252205817</v>
       </c>
-      <c r="AH29" s="0">
+      <c r="AK29" s="0">
         <v>0.29613695774238835</v>
       </c>
-      <c r="AI29" s="0">
+      <c r="AL29" s="0">
         <v>-0.044607001535815649</v>
       </c>
-      <c r="AJ29" s="0">
+      <c r="AM29" s="0">
         <v>2031</v>
       </c>
     </row>
@@ -10045,7 +10876,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>20</v>
@@ -10064,7 +10895,7 @@
         <v>10</v>
       </c>
       <c r="I30" s="0">
-        <v>1.088515258184817</v>
+        <v>1.0866253899989111</v>
       </c>
       <c r="J30" s="0">
         <v>5.53042749383631</v>
@@ -10073,28 +10904,28 @@
         <v>0.096524168810262018</v>
       </c>
       <c r="L30" s="0">
-        <v>0.24410124272463915</v>
+        <v>0.24181061149927005</v>
       </c>
       <c r="M30" s="0">
-        <v>1.565</v>
+        <v>1.5660000000000001</v>
       </c>
       <c r="N30" s="0">
-        <v>2.6118833277853071</v>
+        <v>2.6000450470115206</v>
       </c>
       <c r="O30" s="0">
-        <v>0.00064565567284280423</v>
+        <v>0.0007022084268497597</v>
       </c>
       <c r="P30" s="0">
-        <v>2.8090000000000002</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="Q30" s="0">
-        <v>0.031217078044695534</v>
+        <v>0.030256374553481846</v>
       </c>
       <c r="R30" s="0">
-        <v>0.82305292180626066</v>
+        <v>0.82299636905225371</v>
       </c>
       <c r="S30" s="0">
-        <v>0.39701568974800633</v>
+        <v>0.45270657177081963</v>
       </c>
       <c r="T30" s="0">
         <v>0.049500000000000072</v>
@@ -10106,45 +10937,54 @@
         <v>0.00076711703703047363</v>
       </c>
       <c r="W30" s="0">
-        <v>0.095082899999999998</v>
+        <v>0.012957900000000014</v>
       </c>
       <c r="X30" s="0">
-        <v>9.5073392660733926</v>
+        <v>12.944955044955059</v>
       </c>
       <c r="Y30" s="0">
+        <v>0.093832899999999997</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB30" s="0">
         <v>5</v>
       </c>
-      <c r="Z30" s="0">
+      <c r="AC30" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA30" s="0">
+      <c r="AD30" s="0">
         <v>-0.024215858070456051</v>
       </c>
-      <c r="AB30" s="0">
+      <c r="AE30" s="0">
         <v>0.035686249116920227</v>
       </c>
-      <c r="AC30" s="0">
+      <c r="AF30" s="0">
         <v>-0.058777780448417444</v>
       </c>
-      <c r="AD30" s="0">
+      <c r="AG30" s="0">
         <v>5.53042749383631</v>
       </c>
-      <c r="AE30" s="0">
+      <c r="AH30" s="0">
         <v>0.82369857747910347</v>
       </c>
-      <c r="AF30" s="0">
+      <c r="AI30" s="0">
         <v>-5.115526398965244</v>
       </c>
-      <c r="AG30" s="0">
+      <c r="AJ30" s="0">
         <v>4.6670959252205817</v>
       </c>
-      <c r="AH30" s="0">
+      <c r="AK30" s="0">
         <v>0.29613695774238835</v>
       </c>
-      <c r="AI30" s="0">
+      <c r="AL30" s="0">
         <v>-0.044607001535815649</v>
       </c>
-      <c r="AJ30" s="0">
+      <c r="AM30" s="0">
         <v>2031</v>
       </c>
     </row>
@@ -10153,7 +10993,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>20</v>
@@ -10172,7 +11012,7 @@
         <v>10</v>
       </c>
       <c r="I31" s="0">
-        <v>1.3266315732323786</v>
+        <v>1.3268289816014716</v>
       </c>
       <c r="J31" s="0">
         <v>5.53042749383631</v>
@@ -10181,28 +11021,28 @@
         <v>0.096524168810262018</v>
       </c>
       <c r="L31" s="0">
-        <v>0.3122685292596068</v>
+        <v>0.31008955952027772</v>
       </c>
       <c r="M31" s="0">
-        <v>1.8009999999999999</v>
+        <v>1.8029999999999999</v>
       </c>
       <c r="N31" s="0">
-        <v>2.4685844703745987</v>
+        <v>2.4678007823799808</v>
       </c>
       <c r="O31" s="0">
-        <v>0.00020949784908208535</v>
+        <v>0.00025723649761788536</v>
       </c>
       <c r="P31" s="0">
-        <v>2.8260000000000001</v>
+        <v>2.827</v>
       </c>
       <c r="Q31" s="0">
-        <v>0.007350096150748997</v>
+        <v>0.006807453640595873</v>
       </c>
       <c r="R31" s="0">
-        <v>0.82348907963002138</v>
+        <v>0.82344134098148558</v>
       </c>
       <c r="S31" s="0">
-        <v>0.85311156755941409</v>
+        <v>1.0094873763682615</v>
       </c>
       <c r="T31" s="0">
         <v>0.039500000000000229</v>
@@ -10214,45 +11054,54 @@
         <v>0.00076711703703047363</v>
       </c>
       <c r="W31" s="0">
-        <v>0.1145</v>
+        <v>0.028625899999999985</v>
       </c>
       <c r="X31" s="0">
-        <v>11.44885511448855</v>
+        <v>28.597302697302684</v>
       </c>
       <c r="Y31" s="0">
+        <v>0.1124217</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB31" s="0">
         <v>5</v>
       </c>
-      <c r="Z31" s="0">
+      <c r="AC31" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA31" s="0">
+      <c r="AD31" s="0">
         <v>-0.024215858070456051</v>
       </c>
-      <c r="AB31" s="0">
+      <c r="AE31" s="0">
         <v>0.035686249116920227</v>
       </c>
-      <c r="AC31" s="0">
+      <c r="AF31" s="0">
         <v>-0.058777780448417444</v>
       </c>
-      <c r="AD31" s="0">
+      <c r="AG31" s="0">
         <v>5.53042749383631</v>
       </c>
-      <c r="AE31" s="0">
+      <c r="AH31" s="0">
         <v>0.82369857747910347</v>
       </c>
-      <c r="AF31" s="0">
+      <c r="AI31" s="0">
         <v>-5.115526398965244</v>
       </c>
-      <c r="AG31" s="0">
+      <c r="AJ31" s="0">
         <v>4.6670959252205817</v>
       </c>
-      <c r="AH31" s="0">
+      <c r="AK31" s="0">
         <v>0.29613695774238835</v>
       </c>
-      <c r="AI31" s="0">
+      <c r="AL31" s="0">
         <v>-0.044607001535815649</v>
       </c>
-      <c r="AJ31" s="0">
+      <c r="AM31" s="0">
         <v>2031</v>
       </c>
     </row>
@@ -10261,7 +11110,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>20</v>
@@ -10324,45 +11173,54 @@
         <v>10</v>
       </c>
       <c r="W32" s="0">
-        <v>0.096495499999999998</v>
+        <v>0.014646700000000039</v>
       </c>
       <c r="X32" s="0">
-        <v>9.6485851414858512</v>
+        <v>14.632067932067971</v>
       </c>
       <c r="Y32" s="0">
+        <v>0.093584000000000001</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB32" s="0">
         <v>6</v>
       </c>
-      <c r="Z32" s="0">
+      <c r="AC32" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA32" s="0">
+      <c r="AD32" s="0">
         <v>0.091115773991745724</v>
       </c>
-      <c r="AB32" s="0">
+      <c r="AE32" s="0">
         <v>0.076984652519156038</v>
       </c>
-      <c r="AC32" s="0">
+      <c r="AF32" s="0">
         <v>-0.044459354165570057</v>
       </c>
-      <c r="AD32" s="0">
+      <c r="AG32" s="0">
         <v>6.3825482698478062</v>
       </c>
-      <c r="AE32" s="0">
+      <c r="AH32" s="0">
         <v>0.69757804757206665</v>
       </c>
-      <c r="AF32" s="0">
+      <c r="AI32" s="0">
         <v>5.1110238679748754</v>
       </c>
-      <c r="AG32" s="0">
+      <c r="AJ32" s="0">
         <v>3.7867067267193217</v>
       </c>
-      <c r="AH32" s="0">
+      <c r="AK32" s="0">
         <v>0.26649311397426873</v>
       </c>
-      <c r="AI32" s="0">
+      <c r="AL32" s="0">
         <v>-0.41870465399738555</v>
       </c>
-      <c r="AJ32" s="0">
+      <c r="AM32" s="0">
         <v>2032</v>
       </c>
     </row>
@@ -10371,7 +11229,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>20</v>
@@ -10432,45 +11290,54 @@
         <v>0.00080015930640975341</v>
       </c>
       <c r="W33" s="0">
-        <v>0.1029045</v>
+        <v>0.021870600000000084</v>
       </c>
       <c r="X33" s="0">
-        <v>10.289421057894209</v>
+        <v>21.848751248751334</v>
       </c>
       <c r="Y33" s="0">
+        <v>0.10441979999999999</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB33" s="0">
         <v>6</v>
       </c>
-      <c r="Z33" s="0">
+      <c r="AC33" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA33" s="0">
+      <c r="AD33" s="0">
         <v>0.091115773991745724</v>
       </c>
-      <c r="AB33" s="0">
+      <c r="AE33" s="0">
         <v>0.076984652519156038</v>
       </c>
-      <c r="AC33" s="0">
+      <c r="AF33" s="0">
         <v>-0.044459354165570057</v>
       </c>
-      <c r="AD33" s="0">
+      <c r="AG33" s="0">
         <v>6.3825482698478062</v>
       </c>
-      <c r="AE33" s="0">
+      <c r="AH33" s="0">
         <v>0.69757804757206665</v>
       </c>
-      <c r="AF33" s="0">
+      <c r="AI33" s="0">
         <v>5.1110238679748754</v>
       </c>
-      <c r="AG33" s="0">
+      <c r="AJ33" s="0">
         <v>3.7867067267193217</v>
       </c>
-      <c r="AH33" s="0">
+      <c r="AK33" s="0">
         <v>0.26649311397426873</v>
       </c>
-      <c r="AI33" s="0">
+      <c r="AL33" s="0">
         <v>-0.41870465399738555</v>
       </c>
-      <c r="AJ33" s="0">
+      <c r="AM33" s="0">
         <v>2032</v>
       </c>
     </row>
@@ -10479,7 +11346,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>20</v>
@@ -10540,45 +11407,54 @@
         <v>0.00080015930640975341</v>
       </c>
       <c r="W34" s="0">
-        <v>0.1502201</v>
+        <v>0.063317199999999935</v>
       </c>
       <c r="X34" s="0">
-        <v>15.020507949205079</v>
+        <v>63.253946053945981</v>
       </c>
       <c r="Y34" s="0">
+        <v>0.1507223</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB34" s="0">
         <v>6</v>
       </c>
-      <c r="Z34" s="0">
+      <c r="AC34" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA34" s="0">
+      <c r="AD34" s="0">
         <v>0.091115773991745724</v>
       </c>
-      <c r="AB34" s="0">
+      <c r="AE34" s="0">
         <v>0.076984652519156038</v>
       </c>
-      <c r="AC34" s="0">
+      <c r="AF34" s="0">
         <v>-0.044459354165570057</v>
       </c>
-      <c r="AD34" s="0">
+      <c r="AG34" s="0">
         <v>6.3825482698478062</v>
       </c>
-      <c r="AE34" s="0">
+      <c r="AH34" s="0">
         <v>0.69757804757206665</v>
       </c>
-      <c r="AF34" s="0">
+      <c r="AI34" s="0">
         <v>5.1110238679748754</v>
       </c>
-      <c r="AG34" s="0">
+      <c r="AJ34" s="0">
         <v>3.7867067267193217</v>
       </c>
-      <c r="AH34" s="0">
+      <c r="AK34" s="0">
         <v>0.26649311397426873</v>
       </c>
-      <c r="AI34" s="0">
+      <c r="AL34" s="0">
         <v>-0.41870465399738555</v>
       </c>
-      <c r="AJ34" s="0">
+      <c r="AM34" s="0">
         <v>2032</v>
       </c>
     </row>
@@ -10587,7 +11463,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>20</v>
@@ -10606,7 +11482,7 @@
         <v>10</v>
       </c>
       <c r="I35" s="0">
-        <v>0.96712663460989434</v>
+        <v>0.96604285055226469</v>
       </c>
       <c r="J35" s="0">
         <v>6.3825482698478062</v>
@@ -10615,28 +11491,28 @@
         <v>0.11139648197631173</v>
       </c>
       <c r="L35" s="0">
-        <v>0.19098543013892647</v>
+        <v>0.19079883482073087</v>
       </c>
       <c r="M35" s="0">
-        <v>1.516</v>
+        <v>1.5190000000000001</v>
       </c>
       <c r="N35" s="0">
-        <v>2.1696306334148239</v>
+        <v>2.1546701776885429</v>
       </c>
       <c r="O35" s="0">
-        <v>0.0083990578970286611</v>
+        <v>0.0077178713113552622</v>
       </c>
       <c r="P35" s="0">
-        <v>2.617</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="Q35" s="0">
-        <v>0.012994083607705487</v>
+        <v>0.012641361813287122</v>
       </c>
       <c r="R35" s="0">
-        <v>0.70597710546909531</v>
+        <v>0.70529591888342191</v>
       </c>
       <c r="S35" s="0">
-        <v>0.38393677328930137</v>
+        <v>0.46693308243363024</v>
       </c>
       <c r="T35" s="0">
         <v>0.049500000000000072</v>
@@ -10648,45 +11524,54 @@
         <v>0.00080015930640975341</v>
       </c>
       <c r="W35" s="0">
-        <v>0.094946799999999998</v>
+        <v>0.01255429999999999</v>
       </c>
       <c r="X35" s="0">
-        <v>9.4937306269373067</v>
+        <v>12.541758241758233</v>
       </c>
       <c r="Y35" s="0">
+        <v>0.092855999999999994</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB35" s="0">
         <v>6</v>
       </c>
-      <c r="Z35" s="0">
+      <c r="AC35" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA35" s="0">
+      <c r="AD35" s="0">
         <v>0.091115773991745724</v>
       </c>
-      <c r="AB35" s="0">
+      <c r="AE35" s="0">
         <v>0.076984652519156038</v>
       </c>
-      <c r="AC35" s="0">
+      <c r="AF35" s="0">
         <v>-0.044459354165570057</v>
       </c>
-      <c r="AD35" s="0">
+      <c r="AG35" s="0">
         <v>6.3825482698478062</v>
       </c>
-      <c r="AE35" s="0">
+      <c r="AH35" s="0">
         <v>0.69757804757206665</v>
       </c>
-      <c r="AF35" s="0">
+      <c r="AI35" s="0">
         <v>5.1110238679748754</v>
       </c>
-      <c r="AG35" s="0">
+      <c r="AJ35" s="0">
         <v>3.7867067267193217</v>
       </c>
-      <c r="AH35" s="0">
+      <c r="AK35" s="0">
         <v>0.26649311397426873</v>
       </c>
-      <c r="AI35" s="0">
+      <c r="AL35" s="0">
         <v>-0.41870465399738555</v>
       </c>
-      <c r="AJ35" s="0">
+      <c r="AM35" s="0">
         <v>2032</v>
       </c>
     </row>
@@ -10695,7 +11580,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>20</v>
@@ -10714,7 +11599,7 @@
         <v>10</v>
       </c>
       <c r="I36" s="0">
-        <v>1.2318906422323532</v>
+        <v>1.2352172845044664</v>
       </c>
       <c r="J36" s="0">
         <v>6.3825482698478062</v>
@@ -10723,78 +11608,87 @@
         <v>0.11139648197631173</v>
       </c>
       <c r="L36" s="0">
-        <v>0.2886118829669726</v>
+        <v>0.28508395055623165</v>
       </c>
       <c r="M36" s="0">
-        <v>1.774</v>
+        <v>1.7770000000000001</v>
       </c>
       <c r="N36" s="0">
-        <v>2.1145537558285641</v>
+        <v>2.1231288620996285</v>
       </c>
       <c r="O36" s="0">
-        <v>0.00176480187846495</v>
+        <v>0.0018470947233794055</v>
       </c>
       <c r="P36" s="0">
-        <v>2.73</v>
+        <v>2.734</v>
       </c>
       <c r="Q36" s="0">
-        <v>0.0036522480429354021</v>
+        <v>0.0034793986667910337</v>
       </c>
       <c r="R36" s="0">
-        <v>0.6958132456936017</v>
+        <v>0.69573095284868725</v>
       </c>
       <c r="S36" s="0">
-        <v>0.8779115735262536</v>
+        <v>1.1418623928893712</v>
       </c>
       <c r="T36" s="0">
-        <v>0.059500000000000018</v>
+        <v>0.089499999999999608</v>
       </c>
       <c r="U36" s="0">
-        <v>0.0059994000599940004</v>
+        <v>0.0089991000899910002</v>
       </c>
       <c r="V36" s="0">
         <v>0.00080015930640975341</v>
       </c>
       <c r="W36" s="0">
-        <v>0.1195543</v>
+        <v>0.029531999999999874</v>
       </c>
       <c r="X36" s="0">
-        <v>11.954234576542346</v>
+        <v>29.502497502497377</v>
       </c>
       <c r="Y36" s="0">
+        <v>0.1139529</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB36" s="0">
         <v>6</v>
       </c>
-      <c r="Z36" s="0">
+      <c r="AC36" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA36" s="0">
+      <c r="AD36" s="0">
         <v>0.091115773991745724</v>
       </c>
-      <c r="AB36" s="0">
+      <c r="AE36" s="0">
         <v>0.076984652519156038</v>
       </c>
-      <c r="AC36" s="0">
+      <c r="AF36" s="0">
         <v>-0.044459354165570057</v>
       </c>
-      <c r="AD36" s="0">
+      <c r="AG36" s="0">
         <v>6.3825482698478062</v>
       </c>
-      <c r="AE36" s="0">
+      <c r="AH36" s="0">
         <v>0.69757804757206665</v>
       </c>
-      <c r="AF36" s="0">
+      <c r="AI36" s="0">
         <v>5.1110238679748754</v>
       </c>
-      <c r="AG36" s="0">
+      <c r="AJ36" s="0">
         <v>3.7867067267193217</v>
       </c>
-      <c r="AH36" s="0">
+      <c r="AK36" s="0">
         <v>0.26649311397426873</v>
       </c>
-      <c r="AI36" s="0">
+      <c r="AL36" s="0">
         <v>-0.41870465399738555</v>
       </c>
-      <c r="AJ36" s="0">
+      <c r="AM36" s="0">
         <v>2032</v>
       </c>
     </row>
@@ -10803,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>20</v>
@@ -10866,45 +11760,54 @@
         <v>10</v>
       </c>
       <c r="W37" s="0">
-        <v>0.095712400000000003</v>
+        <v>0.014917500000000049</v>
       </c>
       <c r="X37" s="0">
-        <v>9.5702829717028308</v>
+        <v>14.902597402597452</v>
       </c>
       <c r="Y37" s="0">
+        <v>0.094697799999999999</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB37" s="0">
         <v>7</v>
       </c>
-      <c r="Z37" s="0">
+      <c r="AC37" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA37" s="0">
+      <c r="AD37" s="0">
         <v>-0.02346718792428823</v>
       </c>
-      <c r="AB37" s="0">
+      <c r="AE37" s="0">
         <v>0.093573127402658107</v>
       </c>
-      <c r="AC37" s="0">
+      <c r="AF37" s="0">
         <v>0.052403179689944013</v>
       </c>
-      <c r="AD37" s="0">
+      <c r="AG37" s="0">
         <v>4.5298211150082333</v>
       </c>
-      <c r="AE37" s="0">
+      <c r="AH37" s="0">
         <v>0.46168233384192914</v>
       </c>
-      <c r="AF37" s="0">
+      <c r="AI37" s="0">
         <v>-6.5848017404616854</v>
       </c>
-      <c r="AG37" s="0">
+      <c r="AJ37" s="0">
         <v>3.9785909944998754</v>
       </c>
-      <c r="AH37" s="0">
+      <c r="AK37" s="0">
         <v>0.14814130746523313</v>
       </c>
-      <c r="AI37" s="0">
+      <c r="AL37" s="0">
         <v>-0.011485555290430716</v>
       </c>
-      <c r="AJ37" s="0">
+      <c r="AM37" s="0">
         <v>2033</v>
       </c>
     </row>
@@ -10913,7 +11816,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>20</v>
@@ -10974,45 +11877,54 @@
         <v>0.00026769803489123945</v>
       </c>
       <c r="W38" s="0">
-        <v>0.10255</v>
+        <v>0.021397000000000076</v>
       </c>
       <c r="X38" s="0">
-        <v>10.253974602539746</v>
+        <v>21.375624375624451</v>
       </c>
       <c r="Y38" s="0">
+        <v>0.1036571</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB38" s="0">
         <v>7</v>
       </c>
-      <c r="Z38" s="0">
+      <c r="AC38" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA38" s="0">
+      <c r="AD38" s="0">
         <v>-0.02346718792428823</v>
       </c>
-      <c r="AB38" s="0">
+      <c r="AE38" s="0">
         <v>0.093573127402658107</v>
       </c>
-      <c r="AC38" s="0">
+      <c r="AF38" s="0">
         <v>0.052403179689944013</v>
       </c>
-      <c r="AD38" s="0">
+      <c r="AG38" s="0">
         <v>4.5298211150082333</v>
       </c>
-      <c r="AE38" s="0">
+      <c r="AH38" s="0">
         <v>0.46168233384192914</v>
       </c>
-      <c r="AF38" s="0">
+      <c r="AI38" s="0">
         <v>-6.5848017404616854</v>
       </c>
-      <c r="AG38" s="0">
+      <c r="AJ38" s="0">
         <v>3.9785909944998754</v>
       </c>
-      <c r="AH38" s="0">
+      <c r="AK38" s="0">
         <v>0.14814130746523313</v>
       </c>
-      <c r="AI38" s="0">
+      <c r="AL38" s="0">
         <v>-0.011485555290430716</v>
       </c>
-      <c r="AJ38" s="0">
+      <c r="AM38" s="0">
         <v>2033</v>
       </c>
     </row>
@@ -11021,7 +11933,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>20</v>
@@ -11082,45 +11994,54 @@
         <v>0.00026769803489123945</v>
       </c>
       <c r="W39" s="0">
-        <v>0.14898420000000001</v>
+        <v>0.063823099999999924</v>
       </c>
       <c r="X39" s="0">
-        <v>14.896930306969304</v>
+        <v>63.75934065934058</v>
       </c>
       <c r="Y39" s="0">
+        <v>0.15086769999999999</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB39" s="0">
         <v>7</v>
       </c>
-      <c r="Z39" s="0">
+      <c r="AC39" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA39" s="0">
+      <c r="AD39" s="0">
         <v>-0.02346718792428823</v>
       </c>
-      <c r="AB39" s="0">
+      <c r="AE39" s="0">
         <v>0.093573127402658107</v>
       </c>
-      <c r="AC39" s="0">
+      <c r="AF39" s="0">
         <v>0.052403179689944013</v>
       </c>
-      <c r="AD39" s="0">
+      <c r="AG39" s="0">
         <v>4.5298211150082333</v>
       </c>
-      <c r="AE39" s="0">
+      <c r="AH39" s="0">
         <v>0.46168233384192914</v>
       </c>
-      <c r="AF39" s="0">
+      <c r="AI39" s="0">
         <v>-6.5848017404616854</v>
       </c>
-      <c r="AG39" s="0">
+      <c r="AJ39" s="0">
         <v>3.9785909944998754</v>
       </c>
-      <c r="AH39" s="0">
+      <c r="AK39" s="0">
         <v>0.14814130746523313</v>
       </c>
-      <c r="AI39" s="0">
+      <c r="AL39" s="0">
         <v>-0.011485555290430716</v>
       </c>
-      <c r="AJ39" s="0">
+      <c r="AM39" s="0">
         <v>2033</v>
       </c>
     </row>
@@ -11129,7 +12050,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>20</v>
@@ -11148,7 +12069,7 @@
         <v>10</v>
       </c>
       <c r="I40" s="0">
-        <v>0.65263969572064562</v>
+        <v>0.65273925423206591</v>
       </c>
       <c r="J40" s="0">
         <v>4.5298211150082333</v>
@@ -11157,28 +12078,28 @@
         <v>0.079060292983254399</v>
       </c>
       <c r="L40" s="0">
-        <v>0.14633608509124973</v>
+        <v>0.14702983135180606</v>
       </c>
       <c r="M40" s="0">
-        <v>1.3760000000000001</v>
+        <v>1.363</v>
       </c>
       <c r="N40" s="0">
-        <v>1.3836667285325497</v>
+        <v>1.383187760760707</v>
       </c>
       <c r="O40" s="0">
-        <v>0.0027515965336927795</v>
+        <v>0.0027583345246459112</v>
       </c>
       <c r="P40" s="0">
-        <v>2.4889999999999999</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="Q40" s="0">
-        <v>0.012224237872582644</v>
+        <v>0.012172838816644105</v>
       </c>
       <c r="R40" s="0">
-        <v>0.45893073730823636</v>
+        <v>0.45892399931728323</v>
       </c>
       <c r="S40" s="0">
-        <v>0.40308058288750626</v>
+        <v>0.39720229145157748</v>
       </c>
       <c r="T40" s="0">
         <v>0.029500000000000064</v>
@@ -11190,45 +12111,54 @@
         <v>0.00026769803489123945</v>
       </c>
       <c r="W40" s="0">
-        <v>0.0934059</v>
+        <v>0.013731300000000047</v>
       </c>
       <c r="X40" s="0">
-        <v>9.33965603439656</v>
+        <v>13.717582417582463</v>
       </c>
       <c r="Y40" s="0">
+        <v>0.095893900000000004</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB40" s="0">
         <v>7</v>
       </c>
-      <c r="Z40" s="0">
+      <c r="AC40" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA40" s="0">
+      <c r="AD40" s="0">
         <v>-0.02346718792428823</v>
       </c>
-      <c r="AB40" s="0">
+      <c r="AE40" s="0">
         <v>0.093573127402658107</v>
       </c>
-      <c r="AC40" s="0">
+      <c r="AF40" s="0">
         <v>0.052403179689944013</v>
       </c>
-      <c r="AD40" s="0">
+      <c r="AG40" s="0">
         <v>4.5298211150082333</v>
       </c>
-      <c r="AE40" s="0">
+      <c r="AH40" s="0">
         <v>0.46168233384192914</v>
       </c>
-      <c r="AF40" s="0">
+      <c r="AI40" s="0">
         <v>-6.5848017404616854</v>
       </c>
-      <c r="AG40" s="0">
+      <c r="AJ40" s="0">
         <v>3.9785909944998754</v>
       </c>
-      <c r="AH40" s="0">
+      <c r="AK40" s="0">
         <v>0.14814130746523313</v>
       </c>
-      <c r="AI40" s="0">
+      <c r="AL40" s="0">
         <v>-0.011485555290430716</v>
       </c>
-      <c r="AJ40" s="0">
+      <c r="AM40" s="0">
         <v>2033</v>
       </c>
     </row>
@@ -11237,7 +12167,7 @@
         <v>5</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>20</v>
@@ -11256,7 +12186,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="0">
-        <v>0.83616214236227171</v>
+        <v>0.83005275990800165</v>
       </c>
       <c r="J41" s="0">
         <v>4.5298211150082333</v>
@@ -11265,78 +12195,87 @@
         <v>0.079060292983254399</v>
       </c>
       <c r="L41" s="0">
-        <v>0.20823861743049432</v>
+        <v>0.21104844548511636</v>
       </c>
       <c r="M41" s="0">
-        <v>1.631</v>
+        <v>1.6180000000000001</v>
       </c>
       <c r="N41" s="0">
-        <v>1.4096903568025656</v>
+        <v>1.3987535967568317</v>
       </c>
       <c r="O41" s="0">
-        <v>0.00078608808675173503</v>
+        <v>0.00083640952015123782</v>
       </c>
       <c r="P41" s="0">
-        <v>2.5110000000000001</v>
+        <v>2.504</v>
       </c>
       <c r="Q41" s="0">
-        <v>0.0031708279386979399</v>
+        <v>0.003425770306924314</v>
       </c>
       <c r="R41" s="0">
-        <v>0.4608962457551774</v>
+        <v>0.4608459243217779</v>
       </c>
       <c r="S41" s="0">
-        <v>0.91736024537379746</v>
+        <v>0.88312774730883659</v>
       </c>
       <c r="T41" s="0">
-        <v>0.069500000000000936</v>
+        <v>0.059500000000000469</v>
       </c>
       <c r="U41" s="0">
-        <v>0.006999300069993001</v>
+        <v>0.0059994000599940004</v>
       </c>
       <c r="V41" s="0">
         <v>0.00026769803489123945</v>
       </c>
       <c r="W41" s="0">
-        <v>0.1125169</v>
+        <v>0.029284799999999948</v>
       </c>
       <c r="X41" s="0">
-        <v>11.250564943505649</v>
+        <v>29.255544455544403</v>
       </c>
       <c r="Y41" s="0">
+        <v>0.1130698</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB41" s="0">
         <v>7</v>
       </c>
-      <c r="Z41" s="0">
+      <c r="AC41" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA41" s="0">
+      <c r="AD41" s="0">
         <v>-0.02346718792428823</v>
       </c>
-      <c r="AB41" s="0">
+      <c r="AE41" s="0">
         <v>0.093573127402658107</v>
       </c>
-      <c r="AC41" s="0">
+      <c r="AF41" s="0">
         <v>0.052403179689944013</v>
       </c>
-      <c r="AD41" s="0">
+      <c r="AG41" s="0">
         <v>4.5298211150082333</v>
       </c>
-      <c r="AE41" s="0">
+      <c r="AH41" s="0">
         <v>0.46168233384192914</v>
       </c>
-      <c r="AF41" s="0">
+      <c r="AI41" s="0">
         <v>-6.5848017404616854</v>
       </c>
-      <c r="AG41" s="0">
+      <c r="AJ41" s="0">
         <v>3.9785909944998754</v>
       </c>
-      <c r="AH41" s="0">
+      <c r="AK41" s="0">
         <v>0.14814130746523313</v>
       </c>
-      <c r="AI41" s="0">
+      <c r="AL41" s="0">
         <v>-0.011485555290430716</v>
       </c>
-      <c r="AJ41" s="0">
+      <c r="AM41" s="0">
         <v>2033</v>
       </c>
     </row>
@@ -11345,7 +12284,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>20</v>
@@ -11408,45 +12347,54 @@
         <v>10</v>
       </c>
       <c r="W42" s="0">
-        <v>0.093951499999999993</v>
+        <v>0.020739100000000014</v>
       </c>
       <c r="X42" s="0">
-        <v>9.3942105789421042</v>
+        <v>20.718381618381635</v>
       </c>
       <c r="Y42" s="0">
+        <v>0.11362700000000001</v>
+      </c>
+      <c r="Z42" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB42" s="0">
         <v>8</v>
       </c>
-      <c r="Z42" s="0">
+      <c r="AC42" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA42" s="0">
+      <c r="AD42" s="0">
         <v>-0.084156475146802273</v>
       </c>
-      <c r="AB42" s="0">
+      <c r="AE42" s="0">
         <v>0.077290378925458564</v>
       </c>
-      <c r="AC42" s="0">
+      <c r="AF42" s="0">
         <v>0.097383364916472231</v>
       </c>
-      <c r="AD42" s="0">
+      <c r="AG42" s="0">
         <v>4.6169919686866869</v>
       </c>
-      <c r="AE42" s="0">
+      <c r="AH42" s="0">
         <v>0.90603752523563697</v>
       </c>
-      <c r="AF42" s="0">
+      <c r="AI42" s="0">
         <v>6.9312513403439748</v>
       </c>
-      <c r="AG42" s="0">
+      <c r="AJ42" s="0">
         <v>4.5676806624312105</v>
       </c>
-      <c r="AH42" s="0">
+      <c r="AK42" s="0">
         <v>0.16654925505631219</v>
       </c>
-      <c r="AI42" s="0">
+      <c r="AL42" s="0">
         <v>0.34919841997689294</v>
       </c>
-      <c r="AJ42" s="0">
+      <c r="AM42" s="0">
         <v>2034</v>
       </c>
     </row>
@@ -11455,7 +12403,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>20</v>
@@ -11516,45 +12464,54 @@
         <v>0.00077008251247789872</v>
       </c>
       <c r="W43" s="0">
-        <v>0.10246470000000001</v>
+        <v>0.020923400000000151</v>
       </c>
       <c r="X43" s="0">
-        <v>10.245445455454457</v>
+        <v>20.902497502497656</v>
       </c>
       <c r="Y43" s="0">
+        <v>0.1012989</v>
+      </c>
+      <c r="Z43" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB43" s="0">
         <v>8</v>
       </c>
-      <c r="Z43" s="0">
+      <c r="AC43" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA43" s="0">
+      <c r="AD43" s="0">
         <v>-0.084156475146802273</v>
       </c>
-      <c r="AB43" s="0">
+      <c r="AE43" s="0">
         <v>0.077290378925458564</v>
       </c>
-      <c r="AC43" s="0">
+      <c r="AF43" s="0">
         <v>0.097383364916472231</v>
       </c>
-      <c r="AD43" s="0">
+      <c r="AG43" s="0">
         <v>4.6169919686866869</v>
       </c>
-      <c r="AE43" s="0">
+      <c r="AH43" s="0">
         <v>0.90603752523563697</v>
       </c>
-      <c r="AF43" s="0">
+      <c r="AI43" s="0">
         <v>6.9312513403439748</v>
       </c>
-      <c r="AG43" s="0">
+      <c r="AJ43" s="0">
         <v>4.5676806624312105</v>
       </c>
-      <c r="AH43" s="0">
+      <c r="AK43" s="0">
         <v>0.16654925505631219</v>
       </c>
-      <c r="AI43" s="0">
+      <c r="AL43" s="0">
         <v>0.34919841997689294</v>
       </c>
-      <c r="AJ43" s="0">
+      <c r="AM43" s="0">
         <v>2034</v>
       </c>
     </row>
@@ -11563,7 +12520,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>20</v>
@@ -11624,45 +12581,54 @@
         <v>0.00077008251247789872</v>
       </c>
       <c r="W44" s="0">
-        <v>0.14629909999999999</v>
+        <v>0.06059590000000014</v>
       </c>
       <c r="X44" s="0">
-        <v>14.628447155284471</v>
+        <v>60.535364635364779</v>
       </c>
       <c r="Y44" s="0">
+        <v>0.1455419</v>
+      </c>
+      <c r="Z44" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB44" s="0">
         <v>8</v>
       </c>
-      <c r="Z44" s="0">
+      <c r="AC44" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA44" s="0">
+      <c r="AD44" s="0">
         <v>-0.084156475146802273</v>
       </c>
-      <c r="AB44" s="0">
+      <c r="AE44" s="0">
         <v>0.077290378925458564</v>
       </c>
-      <c r="AC44" s="0">
+      <c r="AF44" s="0">
         <v>0.097383364916472231</v>
       </c>
-      <c r="AD44" s="0">
+      <c r="AG44" s="0">
         <v>4.6169919686866869</v>
       </c>
-      <c r="AE44" s="0">
+      <c r="AH44" s="0">
         <v>0.90603752523563697</v>
       </c>
-      <c r="AF44" s="0">
+      <c r="AI44" s="0">
         <v>6.9312513403439748</v>
       </c>
-      <c r="AG44" s="0">
+      <c r="AJ44" s="0">
         <v>4.5676806624312105</v>
       </c>
-      <c r="AH44" s="0">
+      <c r="AK44" s="0">
         <v>0.16654925505631219</v>
       </c>
-      <c r="AI44" s="0">
+      <c r="AL44" s="0">
         <v>0.34919841997689294</v>
       </c>
-      <c r="AJ44" s="0">
+      <c r="AM44" s="0">
         <v>2034</v>
       </c>
     </row>
@@ -11671,7 +12637,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>20</v>
@@ -11690,37 +12656,37 @@
         <v>10</v>
       </c>
       <c r="I45" s="0">
-        <v>1.1581176590379856</v>
+        <v>1.1618074932575255</v>
       </c>
       <c r="J45" s="0">
-        <v>5.4823692166189897</v>
+        <v>5.6010320335952155</v>
       </c>
       <c r="K45" s="0">
-        <v>0.095685393639983601</v>
+        <v>0.097756450495910155</v>
       </c>
       <c r="L45" s="0">
-        <v>0.24326033186199331</v>
+        <v>0.24399794360718433</v>
       </c>
       <c r="M45" s="0">
-        <v>1.6100000000000001</v>
+        <v>1.6060000000000001</v>
       </c>
       <c r="N45" s="0">
-        <v>2.8268603117506199</v>
+        <v>2.8359892446260737</v>
       </c>
       <c r="O45" s="0">
-        <v>0.0059899841679590393</v>
+        <v>0.0061514112683179745</v>
       </c>
       <c r="P45" s="0">
-        <v>2.9420000000000002</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="Q45" s="0">
-        <v>0.0017186059091880423</v>
+        <v>0.0018801091709134132</v>
       </c>
       <c r="R45" s="0">
-        <v>0.90004754106767793</v>
+        <v>0.89988611396731899</v>
       </c>
       <c r="S45" s="0">
-        <v>0.440945521511657</v>
+        <v>0.40090320459069623</v>
       </c>
       <c r="T45" s="0">
         <v>0.049499999999999975</v>
@@ -11732,45 +12698,54 @@
         <v>0.00077008251247789872</v>
       </c>
       <c r="W45" s="0">
-        <v>0.092739000000000002</v>
+        <v>0.012678300000000045</v>
       </c>
       <c r="X45" s="0">
-        <v>9.2729727027297262</v>
+        <v>12.665634365634411</v>
       </c>
       <c r="Y45" s="0">
+        <v>0.093219999999999997</v>
+      </c>
+      <c r="Z45" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB45" s="0">
         <v>8</v>
       </c>
-      <c r="Z45" s="0">
+      <c r="AC45" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA45" s="0">
+      <c r="AD45" s="0">
         <v>-0.084156475146802273</v>
       </c>
-      <c r="AB45" s="0">
+      <c r="AE45" s="0">
         <v>0.077290378925458564</v>
       </c>
-      <c r="AC45" s="0">
+      <c r="AF45" s="0">
         <v>0.097383364916472231</v>
       </c>
-      <c r="AD45" s="0">
+      <c r="AG45" s="0">
         <v>4.6169919686866869</v>
       </c>
-      <c r="AE45" s="0">
+      <c r="AH45" s="0">
         <v>0.90603752523563697</v>
       </c>
-      <c r="AF45" s="0">
+      <c r="AI45" s="0">
         <v>6.9312513403439748</v>
       </c>
-      <c r="AG45" s="0">
+      <c r="AJ45" s="0">
         <v>4.5676806624312105</v>
       </c>
-      <c r="AH45" s="0">
+      <c r="AK45" s="0">
         <v>0.16654925505631219</v>
       </c>
-      <c r="AI45" s="0">
+      <c r="AL45" s="0">
         <v>0.34919841997689294</v>
       </c>
-      <c r="AJ45" s="0">
+      <c r="AM45" s="0">
         <v>2034</v>
       </c>
     </row>
@@ -11779,7 +12754,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>20</v>
@@ -11798,87 +12773,96 @@
         <v>10</v>
       </c>
       <c r="I46" s="0">
-        <v>1.405417629158078</v>
+        <v>1.3955150715333593</v>
       </c>
       <c r="J46" s="0">
-        <v>5.2711528944336541</v>
+        <v>5.3934953203999303</v>
       </c>
       <c r="K46" s="0">
-        <v>0.091998973383896343</v>
+        <v>0.094134251531885274</v>
       </c>
       <c r="L46" s="0">
-        <v>0.33127652835027099</v>
+        <v>0.33652691449188893</v>
       </c>
       <c r="M46" s="0">
-        <v>2.7840000000000003</v>
+        <v>2.7810000000000001</v>
       </c>
       <c r="N46" s="0">
-        <v>2.7420609470476958</v>
+        <v>2.7034045880374098</v>
       </c>
       <c r="O46" s="0">
-        <v>0.0010654877538486263</v>
+        <v>0.0012742446973814658</v>
       </c>
       <c r="P46" s="0">
-        <v>2.907</v>
+        <v>2.8770000000000002</v>
       </c>
       <c r="Q46" s="0">
-        <v>0.0050455654878699407</v>
+        <v>0.0050916124156059617</v>
       </c>
       <c r="R46" s="0">
-        <v>0.90710301298948559</v>
+        <v>0.90731176993301843</v>
       </c>
       <c r="S46" s="0">
-        <v>0.89067301315623126</v>
+        <v>0.76334842082825383</v>
       </c>
       <c r="T46" s="0">
-        <v>0.029500000000000231</v>
+        <v>0.039500000000000229</v>
       </c>
       <c r="U46" s="0">
-        <v>0.0029997000299970002</v>
+        <v>0.0039996000399960003</v>
       </c>
       <c r="V46" s="0">
         <v>0.00077008251247789872</v>
       </c>
       <c r="W46" s="0">
-        <v>0.1114305</v>
+        <v>0.029374799999999968</v>
       </c>
       <c r="X46" s="0">
-        <v>11.141935806419358</v>
+        <v>29.345454545454512</v>
       </c>
       <c r="Y46" s="0">
+        <v>0.11276899999999999</v>
+      </c>
+      <c r="Z46" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB46" s="0">
         <v>8</v>
       </c>
-      <c r="Z46" s="0">
+      <c r="AC46" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA46" s="0">
+      <c r="AD46" s="0">
         <v>-0.084156475146802273</v>
       </c>
-      <c r="AB46" s="0">
+      <c r="AE46" s="0">
         <v>0.077290378925458564</v>
       </c>
-      <c r="AC46" s="0">
+      <c r="AF46" s="0">
         <v>0.097383364916472231</v>
       </c>
-      <c r="AD46" s="0">
+      <c r="AG46" s="0">
         <v>4.6169919686866869</v>
       </c>
-      <c r="AE46" s="0">
+      <c r="AH46" s="0">
         <v>0.90603752523563697</v>
       </c>
-      <c r="AF46" s="0">
+      <c r="AI46" s="0">
         <v>6.9312513403439748</v>
       </c>
-      <c r="AG46" s="0">
+      <c r="AJ46" s="0">
         <v>4.5676806624312105</v>
       </c>
-      <c r="AH46" s="0">
+      <c r="AK46" s="0">
         <v>0.16654925505631219</v>
       </c>
-      <c r="AI46" s="0">
+      <c r="AL46" s="0">
         <v>0.34919841997689294</v>
       </c>
-      <c r="AJ46" s="0">
+      <c r="AM46" s="0">
         <v>2034</v>
       </c>
     </row>
@@ -11887,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>20</v>
@@ -11950,45 +12934,54 @@
         <v>10</v>
       </c>
       <c r="W47" s="0">
-        <v>0.094988500000000003</v>
+        <v>0.014754599999999988</v>
       </c>
       <c r="X47" s="0">
-        <v>9.4979002099790026</v>
+        <v>14.739860139860127</v>
       </c>
       <c r="Y47" s="0">
+        <v>0.094647800000000004</v>
+      </c>
+      <c r="Z47" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB47" s="0">
         <v>9</v>
       </c>
-      <c r="Z47" s="0">
+      <c r="AC47" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA47" s="0">
+      <c r="AD47" s="0">
         <v>-0.069162012874974477</v>
       </c>
-      <c r="AB47" s="0">
+      <c r="AE47" s="0">
         <v>0.064921082411527442</v>
       </c>
-      <c r="AC47" s="0">
+      <c r="AF47" s="0">
         <v>-0.001276557577764903</v>
       </c>
-      <c r="AD47" s="0">
+      <c r="AG47" s="0">
         <v>7.7388424123199382</v>
       </c>
-      <c r="AE47" s="0">
+      <c r="AH47" s="0">
         <v>0.73656483884687429</v>
       </c>
-      <c r="AF47" s="0">
+      <c r="AI47" s="0">
         <v>-5.0815539586222389</v>
       </c>
-      <c r="AG47" s="0">
+      <c r="AJ47" s="0">
         <v>3.570901655730216</v>
       </c>
-      <c r="AH47" s="0">
+      <c r="AK47" s="0">
         <v>0.24159302805142222</v>
       </c>
-      <c r="AI47" s="0">
+      <c r="AL47" s="0">
         <v>-0.010531874437006539</v>
       </c>
-      <c r="AJ47" s="0">
+      <c r="AM47" s="0">
         <v>2035</v>
       </c>
     </row>
@@ -11997,7 +12990,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>20</v>
@@ -12058,45 +13051,54 @@
         <v>0.00050531621836213958</v>
       </c>
       <c r="W48" s="0">
-        <v>0.10456269999999999</v>
+        <v>0.020995300000000244</v>
       </c>
       <c r="X48" s="0">
-        <v>10.455224477552244</v>
+        <v>20.974325674325918</v>
       </c>
       <c r="Y48" s="0">
+        <v>0.1016837</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB48" s="0">
         <v>9</v>
       </c>
-      <c r="Z48" s="0">
+      <c r="AC48" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA48" s="0">
+      <c r="AD48" s="0">
         <v>-0.069162012874974477</v>
       </c>
-      <c r="AB48" s="0">
+      <c r="AE48" s="0">
         <v>0.064921082411527442</v>
       </c>
-      <c r="AC48" s="0">
+      <c r="AF48" s="0">
         <v>-0.001276557577764903</v>
       </c>
-      <c r="AD48" s="0">
+      <c r="AG48" s="0">
         <v>7.7388424123199382</v>
       </c>
-      <c r="AE48" s="0">
+      <c r="AH48" s="0">
         <v>0.73656483884687429</v>
       </c>
-      <c r="AF48" s="0">
+      <c r="AI48" s="0">
         <v>-5.0815539586222389</v>
       </c>
-      <c r="AG48" s="0">
+      <c r="AJ48" s="0">
         <v>3.570901655730216</v>
       </c>
-      <c r="AH48" s="0">
+      <c r="AK48" s="0">
         <v>0.24159302805142222</v>
       </c>
-      <c r="AI48" s="0">
+      <c r="AL48" s="0">
         <v>-0.010531874437006539</v>
       </c>
-      <c r="AJ48" s="0">
+      <c r="AM48" s="0">
         <v>2035</v>
       </c>
     </row>
@@ -12105,7 +13107,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>20</v>
@@ -12166,45 +13168,54 @@
         <v>0.00050531621836213958</v>
       </c>
       <c r="W49" s="0">
-        <v>0.14932500000000001</v>
+        <v>0.060996999999999919</v>
       </c>
       <c r="X49" s="0">
-        <v>14.93100689931007</v>
+        <v>60.936063936063853</v>
       </c>
       <c r="Y49" s="0">
+        <v>0.1466248</v>
+      </c>
+      <c r="Z49" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA49" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB49" s="0">
         <v>9</v>
       </c>
-      <c r="Z49" s="0">
+      <c r="AC49" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA49" s="0">
+      <c r="AD49" s="0">
         <v>-0.069162012874974477</v>
       </c>
-      <c r="AB49" s="0">
+      <c r="AE49" s="0">
         <v>0.064921082411527442</v>
       </c>
-      <c r="AC49" s="0">
+      <c r="AF49" s="0">
         <v>-0.001276557577764903</v>
       </c>
-      <c r="AD49" s="0">
+      <c r="AG49" s="0">
         <v>7.7388424123199382</v>
       </c>
-      <c r="AE49" s="0">
+      <c r="AH49" s="0">
         <v>0.73656483884687429</v>
       </c>
-      <c r="AF49" s="0">
+      <c r="AI49" s="0">
         <v>-5.0815539586222389</v>
       </c>
-      <c r="AG49" s="0">
+      <c r="AJ49" s="0">
         <v>3.570901655730216</v>
       </c>
-      <c r="AH49" s="0">
+      <c r="AK49" s="0">
         <v>0.24159302805142222</v>
       </c>
-      <c r="AI49" s="0">
+      <c r="AL49" s="0">
         <v>-0.010531874437006539</v>
       </c>
-      <c r="AJ49" s="0">
+      <c r="AM49" s="0">
         <v>2035</v>
       </c>
     </row>
@@ -12213,7 +13224,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>20</v>
@@ -12232,7 +13243,7 @@
         <v>10</v>
       </c>
       <c r="I50" s="0">
-        <v>1.0518687749149922</v>
+        <v>1.0510381849406541</v>
       </c>
       <c r="J50" s="0">
         <v>7.7388424123199382</v>
@@ -12241,28 +13252,28 @@
         <v>0.13506828038796351</v>
       </c>
       <c r="L50" s="0">
-        <v>0.20391258981956434</v>
+        <v>0.20413199750283911</v>
       </c>
       <c r="M50" s="0">
-        <v>1.5509999999999999</v>
+        <v>1.5489999999999999</v>
       </c>
       <c r="N50" s="0">
-        <v>2.2168728205048254</v>
+        <v>2.2163125891465736</v>
       </c>
       <c r="O50" s="0">
-        <v>0.0029113477601033777</v>
+        <v>0.0029070552174169651</v>
       </c>
       <c r="P50" s="0">
-        <v>2.754</v>
+        <v>2.7530000000000001</v>
       </c>
       <c r="Q50" s="0">
-        <v>0.021883552664301309</v>
+        <v>0.021734173520397193</v>
       </c>
       <c r="R50" s="0">
-        <v>0.73365349108677092</v>
+        <v>0.73365778362945733</v>
       </c>
       <c r="S50" s="0">
-        <v>0.39852392787521496</v>
+        <v>0.41222801280760862</v>
       </c>
       <c r="T50" s="0">
         <v>0.059500000000000074</v>
@@ -12274,45 +13285,54 @@
         <v>0.00050531621836213958</v>
       </c>
       <c r="W50" s="0">
-        <v>0.092969499999999997</v>
+        <v>0.012583000000000021</v>
       </c>
       <c r="X50" s="0">
-        <v>9.2960203979602039</v>
+        <v>12.570429570429592</v>
       </c>
       <c r="Y50" s="0">
+        <v>0.092661300000000002</v>
+      </c>
+      <c r="Z50" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA50" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB50" s="0">
         <v>9</v>
       </c>
-      <c r="Z50" s="0">
+      <c r="AC50" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA50" s="0">
+      <c r="AD50" s="0">
         <v>-0.069162012874974477</v>
       </c>
-      <c r="AB50" s="0">
+      <c r="AE50" s="0">
         <v>0.064921082411527442</v>
       </c>
-      <c r="AC50" s="0">
+      <c r="AF50" s="0">
         <v>-0.001276557577764903</v>
       </c>
-      <c r="AD50" s="0">
+      <c r="AG50" s="0">
         <v>7.7388424123199382</v>
       </c>
-      <c r="AE50" s="0">
+      <c r="AH50" s="0">
         <v>0.73656483884687429</v>
       </c>
-      <c r="AF50" s="0">
+      <c r="AI50" s="0">
         <v>-5.0815539586222389</v>
       </c>
-      <c r="AG50" s="0">
+      <c r="AJ50" s="0">
         <v>3.570901655730216</v>
       </c>
-      <c r="AH50" s="0">
+      <c r="AK50" s="0">
         <v>0.24159302805142222</v>
       </c>
-      <c r="AI50" s="0">
+      <c r="AL50" s="0">
         <v>-0.010531874437006539</v>
       </c>
-      <c r="AJ50" s="0">
+      <c r="AM50" s="0">
         <v>2035</v>
       </c>
     </row>
@@ -12321,7 +13341,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>20</v>
@@ -12340,7 +13360,7 @@
         <v>10</v>
       </c>
       <c r="I51" s="0">
-        <v>1.3884546931300044</v>
+        <v>1.3810447841043025</v>
       </c>
       <c r="J51" s="0">
         <v>7.7388424123199382</v>
@@ -12349,28 +13369,28 @@
         <v>0.13506828038796351</v>
       </c>
       <c r="L51" s="0">
-        <v>0.2754213420285811</v>
+        <v>0.27663251122461718</v>
       </c>
       <c r="M51" s="0">
-        <v>1.8120000000000001</v>
+        <v>1.804</v>
       </c>
       <c r="N51" s="0">
-        <v>2.2395791697090521</v>
+        <v>2.2236875662205113</v>
       </c>
       <c r="O51" s="0">
-        <v>0.00012443336592282694</v>
+        <v>0.0001264705180995529</v>
       </c>
       <c r="P51" s="0">
-        <v>2.7749999999999999</v>
+        <v>2.7650000000000001</v>
       </c>
       <c r="Q51" s="0">
-        <v>0.0019326021578571773</v>
+        <v>0.0020090124331052506</v>
       </c>
       <c r="R51" s="0">
-        <v>0.73668927221279712</v>
+        <v>0.73669130936497385</v>
       </c>
       <c r="S51" s="0">
-        <v>0.87018778759583193</v>
+        <v>0.89333291815277594</v>
       </c>
       <c r="T51" s="0">
         <v>0.06950000000000002</v>
@@ -12382,45 +13402,54 @@
         <v>0.00050531621836213958</v>
       </c>
       <c r="W51" s="0">
-        <v>0.11485099999999999</v>
+        <v>0.029171799999999887</v>
       </c>
       <c r="X51" s="0">
-        <v>11.483951604839515</v>
+        <v>29.142657342657227</v>
       </c>
       <c r="Y51" s="0">
+        <v>0.1125244</v>
+      </c>
+      <c r="Z51" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AA51" s="0">
+        <v>1001</v>
+      </c>
+      <c r="AB51" s="0">
         <v>9</v>
       </c>
-      <c r="Z51" s="0">
+      <c r="AC51" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="AA51" s="0">
+      <c r="AD51" s="0">
         <v>-0.069162012874974477</v>
       </c>
-      <c r="AB51" s="0">
+      <c r="AE51" s="0">
         <v>0.064921082411527442</v>
       </c>
-      <c r="AC51" s="0">
+      <c r="AF51" s="0">
         <v>-0.001276557577764903</v>
       </c>
-      <c r="AD51" s="0">
+      <c r="AG51" s="0">
         <v>7.7388424123199382</v>
       </c>
-      <c r="AE51" s="0">
+      <c r="AH51" s="0">
         <v>0.73656483884687429</v>
       </c>
-      <c r="AF51" s="0">
+      <c r="AI51" s="0">
         <v>-5.0815539586222389</v>
       </c>
-      <c r="AG51" s="0">
+      <c r="AJ51" s="0">
         <v>3.570901655730216</v>
       </c>
-      <c r="AH51" s="0">
+      <c r="AK51" s="0">
         <v>0.24159302805142222</v>
       </c>
-      <c r="AI51" s="0">
+      <c r="AL51" s="0">
         <v>-0.010531874437006539</v>
       </c>
-      <c r="AJ51" s="0">
+      <c r="AM51" s="0">
         <v>2035</v>
       </c>
     </row>
@@ -12435,19 +13464,19 @@
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
     <col min="2" max="2" width="20.000000" customWidth="true"/>
-    <col min="3" max="3" width="2.90625" customWidth="true"/>
+    <col min="3" max="3" width="12.000000" customWidth="true"/>
     <col min="4" max="4" width="14.453125" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
     <col min="6" max="6" width="15.453125" customWidth="true"/>
     <col min="7" max="7" width="13.453125" customWidth="true"/>
     <col min="8" max="8" width="13.453125" customWidth="true"/>
-    <col min="9" max="9" width="15.36328125" customWidth="true"/>
-    <col min="10" max="10" width="15.90625" customWidth="true"/>
-    <col min="11" max="11" width="6.81640625" customWidth="true"/>
-    <col min="12" max="12" width="12.81640625" customWidth="true"/>
-    <col min="13" max="13" width="11.453125" customWidth="true"/>
-    <col min="14" max="14" width="13.36328125" customWidth="true"/>
-    <col min="15" max="15" width="13.90625" customWidth="true"/>
+    <col min="9" max="9" width="20.000000" customWidth="true"/>
+    <col min="10" max="10" width="21.000000" customWidth="true"/>
+    <col min="11" max="11" width="12.000000" customWidth="true"/>
+    <col min="12" max="12" width="17.000000" customWidth="true"/>
+    <col min="13" max="13" width="16.000000" customWidth="true"/>
+    <col min="14" max="14" width="18.000000" customWidth="true"/>
+    <col min="15" max="15" width="19.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12455,46 +13484,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -13016,25 +14045,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="0">
-        <v>0.96797005172828765</v>
+        <v>0.96943513361386946</v>
       </c>
       <c r="E14" s="0">
-        <v>0.95621186390002444</v>
+        <v>0.95609922798950109</v>
       </c>
       <c r="F14" s="0">
-        <v>0.18988983878135032</v>
+        <v>0.18972856840526695</v>
       </c>
       <c r="G14" s="0">
-        <v>0.81717964977435143</v>
+        <v>0.81930736400975257</v>
       </c>
       <c r="H14" s="0">
-        <v>1.088515258184817</v>
+        <v>1.0866253899989111</v>
       </c>
       <c r="I14" s="0">
-        <v>0.86006555876487811</v>
+        <v>0.86204457246483735</v>
       </c>
       <c r="J14" s="0">
-        <v>1.0705170808535758</v>
+        <v>1.0723121281571215</v>
       </c>
       <c r="K14" s="0">
         <v>10</v>
@@ -13063,25 +14092,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="0">
-        <v>2.213353977863588</v>
+        <v>2.2188497449247899</v>
       </c>
       <c r="E15" s="0">
-        <v>2.1932517269598249</v>
+        <v>2.185491383417558</v>
       </c>
       <c r="F15" s="0">
-        <v>0.48315466958633296</v>
+        <v>0.482845073985742</v>
       </c>
       <c r="G15" s="0">
-        <v>1.858432497892379</v>
+        <v>1.8772803477324269</v>
       </c>
       <c r="H15" s="0">
-        <v>2.6118833277853071</v>
+        <v>2.6000450470115206</v>
       </c>
       <c r="I15" s="0">
-        <v>1.9169777781458397</v>
+        <v>1.9231550440579983</v>
       </c>
       <c r="J15" s="0">
-        <v>2.5149251233957792</v>
+        <v>2.5271766176139776</v>
       </c>
       <c r="K15" s="0">
         <v>10</v>
@@ -13110,25 +14139,25 @@
         <v>10</v>
       </c>
       <c r="D16" s="0">
-        <v>0.4392761491640142</v>
+        <v>0.42090398928932854</v>
       </c>
       <c r="E16" s="0">
-        <v>0.42318913348359555</v>
+        <v>0.40936166794931289</v>
       </c>
       <c r="F16" s="0">
-        <v>0.055154430688740944</v>
+        <v>0.033266734200384965</v>
       </c>
       <c r="G16" s="0">
-        <v>0.39852392787521496</v>
+        <v>0.39720229145157748</v>
       </c>
       <c r="H16" s="0">
-        <v>0.4722449454772662</v>
+        <v>0.45270657177081963</v>
       </c>
       <c r="I16" s="0">
-        <v>0.40874303941218343</v>
+        <v>0.40008074911738617</v>
       </c>
       <c r="J16" s="0">
-        <v>0.47076502078130555</v>
+        <v>0.44004445980335882</v>
       </c>
       <c r="K16" s="0">
         <v>10</v>
@@ -13204,25 +14233,25 @@
         <v>10</v>
       </c>
       <c r="D18" s="0">
-        <v>1.2142020697290377</v>
+        <v>1.210418388529066</v>
       </c>
       <c r="E18" s="0">
-        <v>1.2379557255403808</v>
+        <v>1.2378985867924339</v>
       </c>
       <c r="F18" s="0">
-        <v>0.23404635285728601</v>
+        <v>0.23232088636144557</v>
       </c>
       <c r="G18" s="0">
-        <v>1.0650777423364191</v>
+        <v>1.0583838238887415</v>
       </c>
       <c r="H18" s="0">
-        <v>1.3884546931300044</v>
+        <v>1.3810447841043025</v>
       </c>
       <c r="I18" s="0">
-        <v>1.0770521725968323</v>
+        <v>1.0744824515411493</v>
       </c>
       <c r="J18" s="0">
-        <v>1.3579653389337687</v>
+        <v>1.3524231478361148</v>
       </c>
       <c r="K18" s="0">
         <v>10</v>
@@ -13251,25 +14280,25 @@
         <v>10</v>
       </c>
       <c r="D19" s="0">
-        <v>2.1713128701489857</v>
+        <v>2.1582349682432458</v>
       </c>
       <c r="E19" s="0">
-        <v>2.1050639739676398</v>
+        <v>2.102993995314971</v>
       </c>
       <c r="F19" s="0">
-        <v>0.47525956331629082</v>
+        <v>0.46939119108688637</v>
       </c>
       <c r="G19" s="0">
-        <v>1.837701004874708</v>
+        <v>1.8240369896123307</v>
       </c>
       <c r="H19" s="0">
-        <v>2.4685844703745987</v>
+        <v>2.4678007823799808</v>
       </c>
       <c r="I19" s="0">
-        <v>1.9109334024477291</v>
+        <v>1.8988849251508584</v>
       </c>
       <c r="J19" s="0">
-        <v>2.450772633468838</v>
+        <v>2.4304786053629881</v>
       </c>
       <c r="K19" s="0">
         <v>10</v>
@@ -13298,25 +14327,25 @@
         <v>10</v>
       </c>
       <c r="D20" s="0">
-        <v>0.96276214250996106</v>
+        <v>0.90755236635491232</v>
       </c>
       <c r="E20" s="0">
-        <v>0.92622374981746569</v>
+        <v>0.88823033273080632</v>
       </c>
       <c r="F20" s="0">
-        <v>0.10677494980171254</v>
+        <v>0.11282567634132361</v>
       </c>
       <c r="G20" s="0">
-        <v>0.8779115735262536</v>
+        <v>0.82339773409762151</v>
       </c>
       <c r="H20" s="0">
-        <v>1.0601207170746374</v>
+        <v>0.97975727482492447</v>
       </c>
       <c r="I20" s="0">
-        <v>0.89578175100182311</v>
+        <v>0.86199469798285156</v>
       </c>
       <c r="J20" s="0">
-        <v>1.0270490657289379</v>
+        <v>0.97588681735267646</v>
       </c>
       <c r="K20" s="0">
         <v>10</v>
@@ -13345,25 +14374,25 @@
         <v>10</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0060993900609938988</v>
+        <v>0.006199380061993799</v>
       </c>
       <c r="E21" s="0">
-        <v>0.006999300069993001</v>
+        <v>0.0064993500649935011</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0020787876051745059</v>
+        <v>0.0018736085488191441</v>
       </c>
       <c r="G21" s="0">
         <v>0.0039996000399960003</v>
       </c>
       <c r="H21" s="0">
-        <v>0.006999300069993001</v>
+        <v>0.0079992000799920006</v>
       </c>
       <c r="I21" s="0">
         <v>0.0050994900509948992</v>
       </c>
       <c r="J21" s="0">
-        <v>0.0072992700729926988</v>
+        <v>0.0070992900709928985</v>
       </c>
       <c r="K21" s="0">
         <v>10</v>
@@ -13387,27 +14416,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.000000" customWidth="true"/>
-    <col min="2" max="2" width="11.54296875" customWidth="true"/>
-    <col min="3" max="3" width="11.36328125" customWidth="true"/>
-    <col min="4" max="4" width="15.08984375" customWidth="true"/>
+    <col min="2" max="2" width="15.000000" customWidth="true"/>
+    <col min="3" max="3" width="16.000000" customWidth="true"/>
+    <col min="4" max="4" width="15.089844" customWidth="true"/>
+    <col min="5" max="5" width="26.000000" customWidth="true"/>
+    <col min="6" max="6" width="24.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -13423,6 +14460,12 @@
       <c r="D2" s="0">
         <v>1.8782718052261252e-06</v>
       </c>
+      <c r="E2" s="0">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -13435,7 +14478,13 @@
         <v>40</v>
       </c>
       <c r="D3" s="0">
-        <v>0.01879557619340615</v>
+        <v>0.021400813720513872</v>
+      </c>
+      <c r="E3" s="0">
+        <v>5</v>
+      </c>
+      <c r="F3" s="0">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -13449,7 +14498,13 @@
         <v>40</v>
       </c>
       <c r="D4" s="0">
-        <v>1.5669678828660468e-07</v>
+        <v>1.6777515340749136e-07</v>
+      </c>
+      <c r="E4" s="0">
+        <v>5</v>
+      </c>
+      <c r="F4" s="0">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -13463,7 +14518,13 @@
         <v>40</v>
       </c>
       <c r="D5" s="0">
-        <v>2.7797789015984935e-05</v>
+        <v>2.1239462614603889e-05</v>
+      </c>
+      <c r="E5" s="0">
+        <v>5</v>
+      </c>
+      <c r="F5" s="0">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13478,37 +14539,37 @@
     <col min="1" max="1" width="20.000000" customWidth="true"/>
     <col min="2" max="2" width="20.000000" customWidth="true"/>
     <col min="3" max="3" width="21.000000" customWidth="true"/>
-    <col min="4" max="4" width="6.26953125" customWidth="true"/>
-    <col min="5" max="5" width="8.90625" customWidth="true"/>
+    <col min="4" max="4" width="12.000000" customWidth="true"/>
+    <col min="5" max="5" width="12.000000" customWidth="true"/>
     <col min="6" max="6" width="15.453125" customWidth="true"/>
-    <col min="7" max="7" width="15.453125" customWidth="true"/>
-    <col min="8" max="8" width="9.90625" customWidth="true"/>
+    <col min="7" max="7" width="16.000000" customWidth="true"/>
+    <col min="8" max="8" width="16.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D1" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>72</v>
-      </c>
       <c r="G1" s="0" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2">
@@ -13896,13 +14957,13 @@
         <v>10</v>
       </c>
       <c r="F18" s="0">
-        <v>0.18587673236587593</v>
+        <v>0.21229383619233158</v>
       </c>
       <c r="G18" s="0">
         <v>0.56186019263342002</v>
       </c>
       <c r="H18" s="0">
-        <v>-0.35999999999999999</v>
+        <v>-0.34000000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -13922,13 +14983,13 @@
         <v>10</v>
       </c>
       <c r="F19" s="0">
-        <v>0.0072845570094796693</v>
+        <v>0.0091084963980309699</v>
       </c>
       <c r="G19" s="0">
-        <v>0.043707342056878012</v>
+        <v>0.05465097838818582</v>
       </c>
       <c r="H19" s="0">
-        <v>-0.71999999999999997</v>
+        <v>-0.69999999999999996</v>
       </c>
     </row>
     <row r="20">
@@ -13974,13 +15035,13 @@
         <v>10</v>
       </c>
       <c r="F21" s="0">
-        <v>0.79133678010066044</v>
+        <v>0.73372999569624731</v>
       </c>
       <c r="G21" s="0">
-        <v>0.79133678010066044</v>
+        <v>0.73372999569624731</v>
       </c>
       <c r="H21" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -14083,7 +15144,7 @@
         <v>0.0022022199424970835</v>
       </c>
       <c r="G26" s="0">
-        <v>0.0022022199424970835</v>
+        <v>0.0026298893394264343</v>
       </c>
       <c r="H26" s="0">
         <v>-0.81999999999999995</v>
@@ -14158,13 +15219,13 @@
         <v>10</v>
       </c>
       <c r="F29" s="0">
-        <v>0.0010079762403767468</v>
+        <v>0.0013149446697132171</v>
       </c>
       <c r="G29" s="0">
-        <v>0.0020159524807534935</v>
+        <v>0.0026298893394264343</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.88</v>
+        <v>-0.85999999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -14368,7 +15429,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="0">
-        <v>0.00014417610153880469</v>
+        <v>0.00014851370472994244</v>
       </c>
       <c r="G38" s="0">
         <v>0.00081471196709260421</v>
@@ -14397,7 +15458,7 @@
         <v>0.088401921504573447</v>
       </c>
       <c r="G39" s="0">
-        <v>0.19323303975842945</v>
+        <v>0.17680384300914689</v>
       </c>
       <c r="H39" s="0">
         <v>-0.45000000000000001</v>
@@ -14420,13 +15481,13 @@
         <v>10</v>
       </c>
       <c r="F40" s="0">
-        <v>0.064411013252809818</v>
+        <v>0.029074539663715</v>
       </c>
       <c r="G40" s="0">
-        <v>0.19323303975842945</v>
+        <v>0.087223618991145002</v>
       </c>
       <c r="H40" s="0">
-        <v>-0.48999999999999999</v>
+        <v>-0.57999999999999996</v>
       </c>
     </row>
     <row r="41">
@@ -14446,13 +15507,13 @@
         <v>10</v>
       </c>
       <c r="F41" s="0">
-        <v>0.23415767169994195</v>
+        <v>0.29747006971910661</v>
       </c>
       <c r="G41" s="0">
-        <v>0.23415767169994195</v>
+        <v>0.29747006971910661</v>
       </c>
       <c r="H41" s="0">
-        <v>-0.32000000000000001</v>
+        <v>-0.28000000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -14465,10 +15526,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
-    <col min="2" max="2" width="4.90625" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="20.7265625" customWidth="true"/>
-    <col min="5" max="5" width="19.453125" customWidth="true"/>
+    <col min="2" max="2" width="12.000000" customWidth="true"/>
+    <col min="3" max="3" width="17.000000" customWidth="true"/>
+    <col min="4" max="4" width="24.000000" customWidth="true"/>
+    <col min="5" max="5" width="23.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14476,16 +15537,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">
@@ -14496,10 +15557,10 @@
         <v>1000</v>
       </c>
       <c r="C2" s="0">
-        <v>0.015931899999999999</v>
+        <v>0.015943800000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>15.931899999999999</v>
+        <v>15.943800000000001</v>
       </c>
       <c r="E2" s="0">
         <v>3</v>
@@ -14513,10 +15574,10 @@
         <v>1000</v>
       </c>
       <c r="C3" s="0">
-        <v>0.023732199999999999</v>
+        <v>0.020846099999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>23.732199999999999</v>
+        <v>20.8461</v>
       </c>
       <c r="E3" s="0">
         <v>5</v>
@@ -14530,10 +15591,10 @@
         <v>1000</v>
       </c>
       <c r="C4" s="0">
-        <v>0.091898300000000002</v>
+        <v>0.069215100000000002</v>
       </c>
       <c r="D4" s="0">
-        <v>91.898300000000006</v>
+        <v>69.215100000000007</v>
       </c>
       <c r="E4" s="0">
         <v>9</v>
@@ -14547,10 +15608,10 @@
         <v>1000</v>
       </c>
       <c r="C5" s="0">
-        <v>0.0096833000000000006</v>
+        <v>0.010661199999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>9.6833000000000009</v>
+        <v>10.661199999999999</v>
       </c>
       <c r="E5" s="0">
         <v>5</v>
@@ -14564,10 +15625,10 @@
         <v>1000</v>
       </c>
       <c r="C6" s="0">
-        <v>0.029556099999999998</v>
+        <v>0.027375799999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>29.556100000000001</v>
+        <v>27.375799999999998</v>
       </c>
       <c r="E6" s="0">
         <v>6</v>
@@ -14583,11 +15644,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
-    <col min="2" max="2" width="4.81640625" customWidth="true"/>
-    <col min="3" max="3" width="13.453125" customWidth="true"/>
+    <col min="2" max="2" width="12.000000" customWidth="true"/>
+    <col min="3" max="3" width="17.000000" customWidth="true"/>
     <col min="4" max="4" width="125.269531" customWidth="true"/>
-    <col min="5" max="5" width="15.36328125" customWidth="true"/>
-    <col min="6" max="6" width="15.08984375" customWidth="true"/>
+    <col min="5" max="5" width="20.000000" customWidth="true"/>
+    <col min="6" max="6" width="19.000000" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14598,16 +15659,16 @@
         <v>21</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
@@ -14621,13 +15682,13 @@
         <v>167.00471383386409</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E2" s="0">
         <v>240</v>
       </c>
       <c r="F2" s="0">
-        <v>56.277425600000001</v>
+        <v>56.668275199999997</v>
       </c>
     </row>
     <row r="3">
@@ -14641,13 +15702,13 @@
         <v>0.082489944444189001</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E3" s="0">
         <v>240</v>
       </c>
       <c r="F3" s="0">
-        <v>47.121687799999997</v>
+        <v>47.8771141</v>
       </c>
     </row>
     <row r="4">
@@ -14661,13 +15722,13 @@
         <v>0.099002209478316894</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E4" s="0">
         <v>240</v>
       </c>
       <c r="F4" s="0">
-        <v>70.817542399999994</v>
+        <v>72.1046008</v>
       </c>
     </row>
     <row r="5">
@@ -14681,13 +15742,13 @@
         <v>0.071561774476849943</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E5" s="0">
         <v>240</v>
       </c>
       <c r="F5" s="0">
-        <v>64.246524399999999</v>
+        <v>65.279228799999999</v>
       </c>
     </row>
     <row r="6">
@@ -14701,13 +15762,13 @@
         <v>0.070483788909463663</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E6" s="0">
         <v>240</v>
       </c>
       <c r="F6" s="0">
-        <v>76.959347800000003</v>
+        <v>77.985353399999994</v>
       </c>
     </row>
   </sheetData>
@@ -14720,7 +15781,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.000000" customWidth="true"/>
-    <col min="2" max="2" width="15.26953125" customWidth="true"/>
+    <col min="2" max="2" width="19.000000" customWidth="true"/>
     <col min="3" max="3" width="14.453125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -14729,10 +15790,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
